--- a/Data/2025-05-29 Public Bodies Directory 2023_24.xlsx
+++ b/Data/2025-05-29 Public Bodies Directory 2023_24.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2554" uniqueCount="2554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2557" uniqueCount="2557">
   <si>
     <t xml:space="preserve">Public Bodies Directory 2023/24</t>
   </si>
@@ -4756,6 +4756,9 @@
   </si>
   <si>
     <t xml:space="preserve">Amanda Pritchard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabinet Office Note: Grant spending data taken from Annual Reports and Accounts: Grants to other bodies + funding to group bodies</t>
   </si>
   <si>
     <t xml:space="preserve">NHS Pay Review Body</t>
@@ -7799,6 +7802,13 @@
   </si>
   <si>
     <t xml:space="preserve">Data for Forestry Commission, Forest Research, and Trinity House has been updated following a retrospective quality assurance review. Staffing figures for the Forestry Commission and Forest Research were corrected to align with Cabinet Office definitions, removing contingent labour from permanent FTE counts and resolving consolidated reporting overlaps. Additionally, data for Trinity House (previously missing) has been populated using proxied values from their 2023-24 Annual Report and Accounts to ensure landscape completeness.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revision to grants/grant-in-aid spending by NHS England to ensure consistency in type of spend captured. Original value of £177bn replaced with £134,180,771,000 (£134bn), reflecting:  £134,068,351,000 in funding to group bodies + £112,420,000 in grants to other bodies, per NHS England Annual Reports and Accounts for 23/24. 
+Original value of £177bn reflected grant-in-aid funding. This is funding received by NHS England to carry out its duties, which is subsequently used by NHS England for grants and funding for other bodies</t>
   </si>
 </sst>
 </file>
@@ -7960,7 +7970,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="revisions" displayName="revisions" ref="A5:C9" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="revisions" displayName="revisions" ref="A5:C10" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="3">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Type"/>
@@ -9352,7 +9362,7 @@
         <v>163</v>
       </c>
       <c r="B16" s="12" t="n">
-        <v>267921474360.2</v>
+        <v>224921474360.2</v>
       </c>
     </row>
     <row r="17">
@@ -9513,7 +9523,7 @@
         <v>365749599887.637</v>
       </c>
       <c r="M6" s="10" t="n">
-        <v>267921474360.2</v>
+        <v>224921474360.2</v>
       </c>
       <c r="N6" s="10" t="n">
         <v>1428659184.1286</v>
@@ -9701,7 +9711,7 @@
         <v>229590665626.938</v>
       </c>
       <c r="M10" s="10" t="n">
-        <v>192828992506.39</v>
+        <v>149828992506.39</v>
       </c>
       <c r="N10" s="10" t="n">
         <v>682614797.8286</v>
@@ -9966,7 +9976,7 @@
         <v>365749599887.637</v>
       </c>
       <c r="M6" s="10" t="n">
-        <v>267921474360.2</v>
+        <v>224921474360.2</v>
       </c>
       <c r="N6" s="10" t="n">
         <v>1428659184.1286</v>
@@ -10483,7 +10493,7 @@
         <v>175085168796.19</v>
       </c>
       <c r="M17" s="10" t="n">
-        <v>176999844843</v>
+        <v>133999844843</v>
       </c>
       <c r="N17" s="10" t="n">
         <v>239025150.9</v>
@@ -11171,7 +11181,7 @@
         <v>365749599887.637</v>
       </c>
       <c r="M6" s="10" t="n">
-        <v>267921474360.2</v>
+        <v>224921474360.2</v>
       </c>
       <c r="N6" s="10" t="n">
         <v>1428659184.1286</v>
@@ -11406,7 +11416,7 @@
         <v>258281093104.16</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>260025664842</v>
+        <v>217025664842</v>
       </c>
       <c r="N11" s="10" t="n">
         <v>245178855</v>
@@ -33435,7 +33445,7 @@
         <v>-80094000</v>
       </c>
       <c r="AV144" s="10" t="n">
-        <v>177000000000</v>
+        <v>134000000000</v>
       </c>
       <c r="AW144" s="10" t="n">
         <v>185007000</v>
@@ -33446,23 +33456,25 @@
       <c r="AY144" s="10" t="n">
         <v>174197481000</v>
       </c>
-      <c r="AZ144" s="10"/>
+      <c r="AZ144" s="10" t="s">
+        <v>1558</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="s">
         <v>169</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="D145" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>190</v>
@@ -33471,7 +33483,7 @@
         <v>1448</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="I145" s="3" t="s">
         <v>171</v>
@@ -33498,7 +33510,7 @@
         <v>255</v>
       </c>
       <c r="Q145" s="3" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="R145" s="10" t="s">
         <v>764</v>
@@ -33531,7 +33543,7 @@
         <v>294</v>
       </c>
       <c r="AB145" s="3" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="AC145" s="3" t="s">
         <v>225</v>
@@ -33611,16 +33623,16 @@
         <v>169</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="D146" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>190</v>
@@ -33638,7 +33650,7 @@
         <v>300</v>
       </c>
       <c r="K146" s="3" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="L146" s="3" t="s">
         <v>230</v>
@@ -33656,13 +33668,13 @@
         <v>291</v>
       </c>
       <c r="Q146" s="3" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="R146" s="10" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="S146" s="3" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="T146" s="3" t="s">
         <v>225</v>
@@ -33689,7 +33701,7 @@
         <v>248</v>
       </c>
       <c r="AB146" s="3" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="AC146" s="3" t="s">
         <v>225</v>
@@ -33698,7 +33710,7 @@
         <v>74000</v>
       </c>
       <c r="AE146" s="3" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="AF146" s="3" t="s">
         <v>225</v>
@@ -33767,16 +33779,16 @@
         <v>169</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="D147" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>190</v>
@@ -33794,7 +33806,7 @@
         <v>223</v>
       </c>
       <c r="K147" s="3" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="L147" s="3" t="s">
         <v>230</v>
@@ -33812,13 +33824,13 @@
         <v>291</v>
       </c>
       <c r="Q147" s="3" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="R147" s="10" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="S147" s="3" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="T147" s="3" t="s">
         <v>225</v>
@@ -33833,19 +33845,19 @@
         <v>231</v>
       </c>
       <c r="X147" s="10" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="Y147" s="10" t="s">
         <v>233</v>
       </c>
       <c r="Z147" s="10" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="AA147" s="10" t="s">
         <v>248</v>
       </c>
       <c r="AB147" s="3" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="AC147" s="3" t="s">
         <v>225</v>
@@ -33854,7 +33866,7 @@
         <v>63000</v>
       </c>
       <c r="AE147" s="3" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="AF147" s="3" t="s">
         <v>225</v>
@@ -33917,7 +33929,7 @@
         <v>472591013</v>
       </c>
       <c r="AZ147" s="10" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="148">
@@ -33925,22 +33937,22 @@
         <v>169</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="D148" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>187</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="H148" s="3" t="s">
         <v>222</v>
@@ -33970,13 +33982,13 @@
         <v>278</v>
       </c>
       <c r="Q148" s="3" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="R148" s="10" t="s">
         <v>898</v>
       </c>
       <c r="S148" s="3" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="T148" s="3" t="s">
         <v>230</v>
@@ -34000,10 +34012,10 @@
         <v>222</v>
       </c>
       <c r="AA148" s="10" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="AB148" s="3" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="AC148" s="3" t="s">
         <v>225</v>
@@ -34012,7 +34024,7 @@
         <v>27420</v>
       </c>
       <c r="AE148" s="3" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="AF148" s="3" t="s">
         <v>225</v>
@@ -34033,7 +34045,7 @@
         <v>398</v>
       </c>
       <c r="AL148" s="3" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="AM148" s="10" t="n">
         <v>9000000</v>
@@ -34075,7 +34087,7 @@
         <v>8622061.7</v>
       </c>
       <c r="AZ148" s="10" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="149">
@@ -34083,22 +34095,22 @@
         <v>169</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="D149" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>187</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="H149" s="3" t="s">
         <v>222</v>
@@ -34128,13 +34140,13 @@
         <v>278</v>
       </c>
       <c r="Q149" s="3" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="R149" s="10" t="s">
         <v>909</v>
       </c>
       <c r="S149" s="3" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="T149" s="3" t="s">
         <v>230</v>
@@ -34149,19 +34161,19 @@
         <v>222</v>
       </c>
       <c r="X149" s="10" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="Y149" s="10" t="s">
         <v>233</v>
       </c>
       <c r="Z149" s="10" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="AA149" s="10" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="AB149" s="3" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="AC149" s="3" t="s">
         <v>225</v>
@@ -34170,7 +34182,7 @@
         <v>80000</v>
       </c>
       <c r="AE149" s="3" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="AF149" s="3" t="s">
         <v>225</v>
@@ -34233,7 +34245,7 @@
         <v>131693217</v>
       </c>
       <c r="AZ149" s="10" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="150">
@@ -34241,22 +34253,22 @@
         <v>169</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="D150" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>187</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="H150" s="3" t="s">
         <v>222</v>
@@ -34268,7 +34280,7 @@
         <v>300</v>
       </c>
       <c r="K150" s="3" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="L150" s="3" t="s">
         <v>230</v>
@@ -34286,13 +34298,13 @@
         <v>571</v>
       </c>
       <c r="Q150" s="3" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="R150" s="10" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="S150" s="3" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="T150" s="3" t="s">
         <v>230</v>
@@ -34319,16 +34331,16 @@
         <v>248</v>
       </c>
       <c r="AB150" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="AC150" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="AD150" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE150" s="3" t="s">
         <v>1614</v>
-      </c>
-      <c r="AC150" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="AD150" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE150" s="3" t="s">
-        <v>1613</v>
       </c>
       <c r="AF150" s="3" t="s">
         <v>230</v>
@@ -34397,25 +34409,25 @@
         <v>169</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="D151" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>187</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="I151" s="3" t="s">
         <v>176</v>
@@ -34442,13 +34454,13 @@
         <v>278</v>
       </c>
       <c r="Q151" s="3" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="R151" s="10" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="S151" s="3" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="T151" s="3" t="s">
         <v>225</v>
@@ -34475,7 +34487,7 @@
         <v>222</v>
       </c>
       <c r="AB151" s="3" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="AC151" s="3" t="s">
         <v>225</v>
@@ -34484,7 +34496,7 @@
         <v>0</v>
       </c>
       <c r="AE151" s="3" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="AF151" s="3" t="s">
         <v>230</v>
@@ -34547,7 +34559,7 @@
         <v>0</v>
       </c>
       <c r="AZ151" s="10" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="152">
@@ -34555,22 +34567,22 @@
         <v>169</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="D152" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>187</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="H152" s="3" t="s">
         <v>222</v>
@@ -34582,7 +34594,7 @@
         <v>300</v>
       </c>
       <c r="K152" s="3" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="L152" s="3" t="s">
         <v>225</v>
@@ -34600,13 +34612,13 @@
         <v>571</v>
       </c>
       <c r="Q152" s="3" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="R152" s="10" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="S152" s="3" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="T152" s="3" t="s">
         <v>225</v>
@@ -34630,10 +34642,10 @@
         <v>222</v>
       </c>
       <c r="AA152" s="10" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="AB152" s="3" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="AC152" s="3" t="s">
         <v>225</v>
@@ -34642,7 +34654,7 @@
         <v>222400</v>
       </c>
       <c r="AE152" s="3" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="AF152" s="3" t="s">
         <v>225</v>
@@ -34705,7 +34717,7 @@
         <v>4396000</v>
       </c>
       <c r="AZ152" s="10" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="153">
@@ -34713,22 +34725,22 @@
         <v>169</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="D153" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>187</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="H153" s="3" t="s">
         <v>222</v>
@@ -34740,7 +34752,7 @@
         <v>223</v>
       </c>
       <c r="K153" s="3" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="L153" s="3" t="s">
         <v>230</v>
@@ -34758,13 +34770,13 @@
         <v>278</v>
       </c>
       <c r="Q153" s="3" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="R153" s="10" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="S153" s="3" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="T153" s="3" t="s">
         <v>225</v>
@@ -34791,7 +34803,7 @@
         <v>1474</v>
       </c>
       <c r="AB153" s="3" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="AC153" s="3" t="s">
         <v>225</v>
@@ -34800,7 +34812,7 @@
         <v>16000</v>
       </c>
       <c r="AE153" s="3" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="AF153" s="3" t="s">
         <v>225</v>
@@ -34863,7 +34875,7 @@
         <v>166705000</v>
       </c>
       <c r="AZ153" s="10" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="154">
@@ -34871,22 +34883,22 @@
         <v>169</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="D154" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>187</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="H154" s="3" t="s">
         <v>222</v>
@@ -34898,7 +34910,7 @@
         <v>223</v>
       </c>
       <c r="K154" s="3" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="L154" s="3" t="s">
         <v>230</v>
@@ -34916,13 +34928,13 @@
         <v>278</v>
       </c>
       <c r="Q154" s="3" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="R154" s="10" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="S154" s="3" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="T154" s="3" t="s">
         <v>230</v>
@@ -34946,10 +34958,10 @@
         <v>247</v>
       </c>
       <c r="AA154" s="10" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="AB154" s="3" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="AC154" s="3" t="s">
         <v>225</v>
@@ -34958,7 +34970,7 @@
         <v>35000</v>
       </c>
       <c r="AE154" s="3" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="AF154" s="3" t="s">
         <v>225</v>
@@ -34979,7 +34991,7 @@
         <v>398</v>
       </c>
       <c r="AL154" s="3" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="AM154" s="10" t="n">
         <v>234306000</v>
@@ -35027,22 +35039,22 @@
         <v>169</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="D155" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>187</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="H155" s="3" t="s">
         <v>222</v>
@@ -35054,7 +35066,7 @@
         <v>300</v>
       </c>
       <c r="K155" s="3" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="L155" s="3" t="s">
         <v>230</v>
@@ -35072,13 +35084,13 @@
         <v>278</v>
       </c>
       <c r="Q155" s="3" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="R155" s="10" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="S155" s="3" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="T155" s="3" t="s">
         <v>230</v>
@@ -35114,7 +35126,7 @@
         <v>20700</v>
       </c>
       <c r="AE155" s="3" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="AF155" s="3" t="s">
         <v>225</v>
@@ -35177,7 +35189,7 @@
         <v>65824656</v>
       </c>
       <c r="AZ155" s="10" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="156">
@@ -35185,22 +35197,22 @@
         <v>169</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="D156" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>187</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="H156" s="3" t="s">
         <v>222</v>
@@ -35230,13 +35242,13 @@
         <v>278</v>
       </c>
       <c r="Q156" s="3" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="R156" s="10" t="s">
         <v>536</v>
       </c>
       <c r="S156" s="3" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="T156" s="3" t="s">
         <v>230</v>
@@ -35263,7 +35275,7 @@
         <v>1237</v>
       </c>
       <c r="AB156" s="3" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="AC156" s="3" t="s">
         <v>225</v>
@@ -35272,7 +35284,7 @@
         <v>24000</v>
       </c>
       <c r="AE156" s="3" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="AF156" s="3" t="s">
         <v>225</v>
@@ -35335,7 +35347,7 @@
         <v>688832029.388354</v>
       </c>
       <c r="AZ156" s="10" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="157">
@@ -35343,22 +35355,22 @@
         <v>169</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="D157" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>187</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="H157" s="3" t="s">
         <v>222</v>
@@ -35388,13 +35400,13 @@
         <v>571</v>
       </c>
       <c r="Q157" s="3" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="R157" s="10" t="s">
         <v>325</v>
       </c>
       <c r="S157" s="3" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="T157" s="3" t="s">
         <v>230</v>
@@ -35418,10 +35430,10 @@
         <v>233</v>
       </c>
       <c r="AA157" s="10" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="AB157" s="3" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="AC157" s="3" t="s">
         <v>225</v>
@@ -35430,7 +35442,7 @@
         <v>29500</v>
       </c>
       <c r="AE157" s="3" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="AF157" s="3" t="s">
         <v>225</v>
@@ -35451,7 +35463,7 @@
         <v>398</v>
       </c>
       <c r="AL157" s="3" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="AM157" s="10" t="n">
         <v>10268053903</v>
@@ -35493,7 +35505,7 @@
         <v>9331668934.29</v>
       </c>
       <c r="AZ157" s="10" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="158">
@@ -35501,22 +35513,22 @@
         <v>169</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="D158" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>189</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="H158" s="3" t="s">
         <v>222</v>
@@ -35546,13 +35558,13 @@
         <v>266</v>
       </c>
       <c r="Q158" s="3" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="R158" s="10" t="s">
         <v>864</v>
       </c>
       <c r="S158" s="3" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="T158" s="3" t="s">
         <v>225</v>
@@ -35576,10 +35588,10 @@
         <v>233</v>
       </c>
       <c r="AA158" s="10" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="AB158" s="3" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="AC158" s="3" t="s">
         <v>225</v>
@@ -35588,7 +35600,7 @@
         <v>82500</v>
       </c>
       <c r="AE158" s="3" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="AF158" s="3" t="s">
         <v>225</v>
@@ -35657,22 +35669,22 @@
         <v>169</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="D159" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>189</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="H159" s="3" t="s">
         <v>222</v>
@@ -35684,7 +35696,7 @@
         <v>265</v>
       </c>
       <c r="K159" s="3" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="L159" s="3" t="s">
         <v>230</v>
@@ -35702,13 +35714,13 @@
         <v>255</v>
       </c>
       <c r="Q159" s="3" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="R159" s="10" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="S159" s="3" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="T159" s="3" t="s">
         <v>225</v>
@@ -35735,7 +35747,7 @@
         <v>248</v>
       </c>
       <c r="AB159" s="3" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="AC159" s="3" t="s">
         <v>225</v>
@@ -35807,7 +35819,7 @@
         <v>106654</v>
       </c>
       <c r="AZ159" s="10" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="160">
@@ -35815,22 +35827,22 @@
         <v>169</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="D160" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>189</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="H160" s="3" t="s">
         <v>222</v>
@@ -35860,13 +35872,13 @@
         <v>278</v>
       </c>
       <c r="Q160" s="3" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="R160" s="10" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="S160" s="3" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="T160" s="3" t="s">
         <v>230</v>
@@ -35893,7 +35905,7 @@
         <v>248</v>
       </c>
       <c r="AB160" s="3" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="AC160" s="3" t="s">
         <v>225</v>
@@ -35902,7 +35914,7 @@
         <v>80000</v>
       </c>
       <c r="AE160" s="3" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="AF160" s="3" t="s">
         <v>225</v>
@@ -35965,7 +35977,7 @@
         <v>168477000</v>
       </c>
       <c r="AZ160" s="10" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="161">
@@ -35973,22 +35985,22 @@
         <v>169</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="D161" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>189</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="H161" s="3" t="s">
         <v>222</v>
@@ -36018,13 +36030,13 @@
         <v>278</v>
       </c>
       <c r="Q161" s="3" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="R161" s="10" t="s">
         <v>944</v>
       </c>
       <c r="S161" s="3" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="T161" s="3" t="s">
         <v>225</v>
@@ -36051,7 +36063,7 @@
         <v>248</v>
       </c>
       <c r="AB161" s="3" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="AC161" s="3" t="s">
         <v>225</v>
@@ -36060,7 +36072,7 @@
         <v>24000</v>
       </c>
       <c r="AE161" s="3" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="AF161" s="3" t="s">
         <v>225</v>
@@ -36123,7 +36135,7 @@
         <v>17523590</v>
       </c>
       <c r="AZ161" s="10" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="162">
@@ -36131,22 +36143,22 @@
         <v>169</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="D162" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>189</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="H162" s="3" t="s">
         <v>222</v>
@@ -36176,13 +36188,13 @@
         <v>266</v>
       </c>
       <c r="Q162" s="3" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="R162" s="10" t="s">
         <v>1465</v>
       </c>
       <c r="S162" s="3" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="T162" s="3" t="s">
         <v>230</v>
@@ -36197,7 +36209,7 @@
         <v>231</v>
       </c>
       <c r="X162" s="10" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="Y162" s="10" t="s">
         <v>232</v>
@@ -36206,10 +36218,10 @@
         <v>232</v>
       </c>
       <c r="AA162" s="10" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="AB162" s="3" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="AC162" s="3" t="s">
         <v>225</v>
@@ -36218,7 +36230,7 @@
         <v>73840</v>
       </c>
       <c r="AE162" s="3" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="AF162" s="3" t="s">
         <v>225</v>
@@ -36289,22 +36301,22 @@
         <v>169</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="D163" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>189</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="H163" s="3" t="s">
         <v>222</v>
@@ -36334,13 +36346,13 @@
         <v>255</v>
       </c>
       <c r="Q163" s="3" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="R163" s="10" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="S163" s="3" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="T163" s="3" t="s">
         <v>225</v>
@@ -36367,7 +36379,7 @@
         <v>491</v>
       </c>
       <c r="AB163" s="3" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="AC163" s="3" t="s">
         <v>225</v>
@@ -36439,7 +36451,7 @@
         <v>56355</v>
       </c>
       <c r="AZ163" s="10" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="164">
@@ -36447,22 +36459,22 @@
         <v>169</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="D164" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>192</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="H164" s="3" t="s">
         <v>222</v>
@@ -36474,7 +36486,7 @@
         <v>300</v>
       </c>
       <c r="K164" s="3" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="L164" s="3" t="s">
         <v>230</v>
@@ -36492,13 +36504,13 @@
         <v>571</v>
       </c>
       <c r="Q164" s="3" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="R164" s="10" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="S164" s="3" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="T164" s="3" t="s">
         <v>230</v>
@@ -36522,10 +36534,10 @@
         <v>233</v>
       </c>
       <c r="AA164" s="10" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="AB164" s="3" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="AC164" s="3" t="s">
         <v>230</v>
@@ -36534,7 +36546,7 @@
         <v>0</v>
       </c>
       <c r="AE164" s="3" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="AF164" s="3" t="s">
         <v>225</v>
@@ -36597,7 +36609,7 @@
         <v>1053447000</v>
       </c>
       <c r="AZ164" s="10" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="165">
@@ -36605,22 +36617,22 @@
         <v>169</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="D165" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>192</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="H165" s="3" t="s">
         <v>222</v>
@@ -36650,13 +36662,13 @@
         <v>278</v>
       </c>
       <c r="Q165" s="3" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="R165" s="10" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="S165" s="3" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="T165" s="3" t="s">
         <v>230</v>
@@ -36680,10 +36692,10 @@
         <v>282</v>
       </c>
       <c r="AA165" s="10" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="AB165" s="3" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="AC165" s="3" t="s">
         <v>225</v>
@@ -36692,7 +36704,7 @@
         <v>12000</v>
       </c>
       <c r="AE165" s="3" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="AF165" s="3" t="s">
         <v>230</v>
@@ -36755,7 +36767,7 @@
         <v>28444000</v>
       </c>
       <c r="AZ165" s="10" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="166">
@@ -36763,22 +36775,22 @@
         <v>169</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="D166" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>192</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="H166" s="3" t="s">
         <v>222</v>
@@ -36790,7 +36802,7 @@
         <v>300</v>
       </c>
       <c r="K166" s="3" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="L166" s="3" t="s">
         <v>230</v>
@@ -36808,13 +36820,13 @@
         <v>571</v>
       </c>
       <c r="Q166" s="3" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="R166" s="10" t="s">
         <v>405</v>
       </c>
       <c r="S166" s="3" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="T166" s="3" t="s">
         <v>230</v>
@@ -36835,13 +36847,13 @@
         <v>233</v>
       </c>
       <c r="Z166" s="10" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="AA166" s="10" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="AB166" s="3" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="AC166" s="3" t="s">
         <v>225</v>
@@ -36850,7 +36862,7 @@
         <v>0</v>
       </c>
       <c r="AE166" s="3" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="AF166" s="3" t="s">
         <v>225</v>
@@ -36871,7 +36883,7 @@
         <v>398</v>
       </c>
       <c r="AL166" s="3" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="AM166" s="10" t="n">
         <v>1040606</v>
@@ -36919,22 +36931,22 @@
         <v>169</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="D167" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>192</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="H167" s="3" t="s">
         <v>222</v>
@@ -36964,13 +36976,13 @@
         <v>571</v>
       </c>
       <c r="Q167" s="3" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="R167" s="10" t="s">
         <v>536</v>
       </c>
       <c r="S167" s="3" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="T167" s="3" t="s">
         <v>230</v>
@@ -36994,10 +37006,10 @@
         <v>222</v>
       </c>
       <c r="AA167" s="10" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="AB167" s="3" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="AC167" s="3" t="s">
         <v>225</v>
@@ -37006,7 +37018,7 @@
         <v>100000</v>
       </c>
       <c r="AE167" s="3" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="AF167" s="3" t="s">
         <v>230</v>
@@ -37077,22 +37089,22 @@
         <v>169</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="D168" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>192</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="H168" s="3" t="s">
         <v>222</v>
@@ -37122,13 +37134,13 @@
         <v>278</v>
       </c>
       <c r="Q168" s="3" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="R168" s="10" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="S168" s="3" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="T168" s="3" t="s">
         <v>230</v>
@@ -37155,7 +37167,7 @@
         <v>233</v>
       </c>
       <c r="AB168" s="3" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="AC168" s="3" t="s">
         <v>225</v>
@@ -37164,7 +37176,7 @@
         <v>0</v>
       </c>
       <c r="AE168" s="3" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="AF168" s="3" t="s">
         <v>230</v>
@@ -37179,7 +37191,7 @@
         <v>408</v>
       </c>
       <c r="AJ168" s="3" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="AK168" s="3" t="s">
         <v>239</v>
@@ -37227,7 +37239,7 @@
         <v>3088932</v>
       </c>
       <c r="AZ168" s="10" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="169">
@@ -37235,22 +37247,22 @@
         <v>169</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="D169" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>192</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="H169" s="3" t="s">
         <v>222</v>
@@ -37262,7 +37274,7 @@
         <v>300</v>
       </c>
       <c r="K169" s="3" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="L169" s="3" t="s">
         <v>230</v>
@@ -37280,13 +37292,13 @@
         <v>571</v>
       </c>
       <c r="Q169" s="3" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="R169" s="10" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="S169" s="3" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="T169" s="3" t="s">
         <v>230</v>
@@ -37313,7 +37325,7 @@
         <v>248</v>
       </c>
       <c r="AB169" s="3" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="AC169" s="3" t="s">
         <v>225</v>
@@ -37322,7 +37334,7 @@
         <v>0</v>
       </c>
       <c r="AE169" s="3" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="AF169" s="3" t="s">
         <v>225</v>
@@ -37391,22 +37403,22 @@
         <v>169</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="D170" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>192</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="H170" s="3" t="s">
         <v>222</v>
@@ -37436,13 +37448,13 @@
         <v>571</v>
       </c>
       <c r="Q170" s="3" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="R170" s="10" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="S170" s="3" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="T170" s="3" t="s">
         <v>230</v>
@@ -37469,7 +37481,7 @@
         <v>248</v>
       </c>
       <c r="AB170" s="3" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="AC170" s="3" t="s">
         <v>225</v>
@@ -37478,7 +37490,7 @@
         <v>25000</v>
       </c>
       <c r="AE170" s="3" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="AF170" s="3" t="s">
         <v>225</v>
@@ -37541,7 +37553,7 @@
         <v>8855816</v>
       </c>
       <c r="AZ170" s="10" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="171">
@@ -37549,22 +37561,22 @@
         <v>169</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="D171" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>191</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="H171" s="3" t="s">
         <v>222</v>
@@ -37576,7 +37588,7 @@
         <v>265</v>
       </c>
       <c r="K171" s="3" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="L171" s="3" t="s">
         <v>230</v>
@@ -37594,13 +37606,13 @@
         <v>255</v>
       </c>
       <c r="Q171" s="3" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="R171" s="10" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="S171" s="3" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="T171" s="3" t="s">
         <v>230</v>
@@ -37615,7 +37627,7 @@
         <v>231</v>
       </c>
       <c r="X171" s="10" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="Y171" s="10" t="s">
         <v>233</v>
@@ -37627,7 +37639,7 @@
         <v>222</v>
       </c>
       <c r="AB171" s="3" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="AC171" s="3" t="s">
         <v>230</v>
@@ -37636,7 +37648,7 @@
         <v>7342</v>
       </c>
       <c r="AE171" s="3" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="AF171" s="3" t="s">
         <v>230</v>
@@ -37705,22 +37717,22 @@
         <v>169</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="D172" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>191</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="H172" s="3" t="s">
         <v>222</v>
@@ -37732,7 +37744,7 @@
         <v>265</v>
       </c>
       <c r="K172" s="3" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="L172" s="3" t="s">
         <v>230</v>
@@ -37750,13 +37762,13 @@
         <v>255</v>
       </c>
       <c r="Q172" s="3" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="R172" s="10" t="s">
         <v>500</v>
       </c>
       <c r="S172" s="3" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="T172" s="3" t="s">
         <v>225</v>
@@ -37783,7 +37795,7 @@
         <v>222</v>
       </c>
       <c r="AB172" s="3" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="AC172" s="3" t="s">
         <v>230</v>
@@ -37792,7 +37804,7 @@
         <v>6284</v>
       </c>
       <c r="AE172" s="3" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="AF172" s="3" t="s">
         <v>230</v>
@@ -37861,22 +37873,22 @@
         <v>169</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="D173" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>191</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="H173" s="3" t="s">
         <v>222</v>
@@ -37888,7 +37900,7 @@
         <v>265</v>
       </c>
       <c r="K173" s="3" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="L173" s="3" t="s">
         <v>230</v>
@@ -37906,13 +37918,13 @@
         <v>255</v>
       </c>
       <c r="Q173" s="3" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="R173" s="10" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="S173" s="3" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="T173" s="3" t="s">
         <v>230</v>
@@ -37939,7 +37951,7 @@
         <v>222</v>
       </c>
       <c r="AB173" s="3" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="AC173" s="3" t="s">
         <v>230</v>
@@ -37948,7 +37960,7 @@
         <v>8406</v>
       </c>
       <c r="AE173" s="3" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="AF173" s="3" t="s">
         <v>230</v>
@@ -38017,22 +38029,22 @@
         <v>169</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="D174" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>191</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="H174" s="3" t="s">
         <v>222</v>
@@ -38044,7 +38056,7 @@
         <v>265</v>
       </c>
       <c r="K174" s="3" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="L174" s="3" t="s">
         <v>230</v>
@@ -38062,13 +38074,13 @@
         <v>255</v>
       </c>
       <c r="Q174" s="3" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="R174" s="10" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="S174" s="3" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="T174" s="3" t="s">
         <v>225</v>
@@ -38095,7 +38107,7 @@
         <v>222</v>
       </c>
       <c r="AB174" s="3" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="AC174" s="3" t="s">
         <v>230</v>
@@ -38104,7 +38116,7 @@
         <v>6591</v>
       </c>
       <c r="AE174" s="3" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="AF174" s="3" t="s">
         <v>230</v>
@@ -38176,19 +38188,19 @@
         <v>191</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="D175" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>191</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="H175" s="3" t="s">
         <v>222</v>
@@ -38218,13 +38230,13 @@
         <v>255</v>
       </c>
       <c r="Q175" s="3" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="R175" s="10" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="S175" s="3" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="T175" s="3" t="s">
         <v>225</v>
@@ -38236,7 +38248,7 @@
         <v>225</v>
       </c>
       <c r="W175" s="3" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="X175" s="10" t="s">
         <v>234</v>
@@ -38251,7 +38263,7 @@
         <v>248</v>
       </c>
       <c r="AB175" s="3" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="AC175" s="3" t="s">
         <v>225</v>
@@ -38260,7 +38272,7 @@
         <v>70000</v>
       </c>
       <c r="AE175" s="3" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="AF175" s="3" t="s">
         <v>225</v>
@@ -38323,7 +38335,7 @@
         <v>138252000</v>
       </c>
       <c r="AZ175" s="10" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="176">
@@ -38331,22 +38343,22 @@
         <v>169</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="D176" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>193</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="H176" s="3" t="s">
         <v>222</v>
@@ -38376,13 +38388,13 @@
         <v>278</v>
       </c>
       <c r="Q176" s="3" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="R176" s="10" t="s">
         <v>1434</v>
       </c>
       <c r="S176" s="3" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="T176" s="3" t="s">
         <v>230</v>
@@ -38409,7 +38421,7 @@
         <v>222</v>
       </c>
       <c r="AB176" s="3" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="AC176" s="3" t="s">
         <v>230</v>
@@ -38418,7 +38430,7 @@
         <v>27500</v>
       </c>
       <c r="AE176" s="3" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="AF176" s="3" t="s">
         <v>225</v>
@@ -38439,7 +38451,7 @@
         <v>563</v>
       </c>
       <c r="AL176" s="3" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="AM176" s="10" t="n">
         <v>40757815000</v>
@@ -38481,7 +38493,7 @@
         <v>39648678000</v>
       </c>
       <c r="AZ176" s="10" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="177">
@@ -38489,22 +38501,22 @@
         <v>169</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="D177" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>193</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="H177" s="3" t="s">
         <v>193</v>
@@ -38534,13 +38546,13 @@
         <v>226</v>
       </c>
       <c r="Q177" s="3" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="R177" s="10" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="S177" s="3" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="T177" s="3" t="s">
         <v>230</v>
@@ -38567,7 +38579,7 @@
         <v>248</v>
       </c>
       <c r="AB177" s="3" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="AC177" s="3" t="s">
         <v>230</v>
@@ -38576,7 +38588,7 @@
         <v>15000</v>
       </c>
       <c r="AE177" s="3" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="AF177" s="3" t="s">
         <v>225</v>
@@ -38639,7 +38651,7 @@
         <v>291771793</v>
       </c>
       <c r="AZ177" s="10" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="178">
@@ -38647,25 +38659,25 @@
         <v>169</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="D178" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>194</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="I178" s="3" t="s">
         <v>175</v>
@@ -38692,13 +38704,13 @@
         <v>278</v>
       </c>
       <c r="Q178" s="3" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="R178" s="10" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="S178" s="3" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="T178" s="3" t="s">
         <v>230</v>
@@ -38722,10 +38734,10 @@
         <v>233</v>
       </c>
       <c r="AA178" s="10" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="AB178" s="3" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="AC178" s="3" t="s">
         <v>225</v>
@@ -38734,7 +38746,7 @@
         <v>12500</v>
       </c>
       <c r="AE178" s="3" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="AF178" s="3" t="s">
         <v>225</v>
@@ -38797,7 +38809,7 @@
         <v>3047272.66999999</v>
       </c>
       <c r="AZ178" s="10" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="179">
@@ -38805,22 +38817,22 @@
         <v>169</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="D179" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>194</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="H179" s="3" t="s">
         <v>222</v>
@@ -38850,13 +38862,13 @@
         <v>278</v>
       </c>
       <c r="Q179" s="3" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="R179" s="10" t="s">
         <v>245</v>
       </c>
       <c r="S179" s="3" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="T179" s="3" t="s">
         <v>230</v>
@@ -38874,16 +38886,16 @@
         <v>368</v>
       </c>
       <c r="Y179" s="10" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="Z179" s="10" t="s">
         <v>715</v>
       </c>
       <c r="AA179" s="10" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="AB179" s="3" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="AC179" s="3" t="s">
         <v>468</v>
@@ -38892,7 +38904,7 @@
         <v>22500</v>
       </c>
       <c r="AE179" s="3" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="AF179" s="3" t="s">
         <v>225</v>
@@ -38955,7 +38967,7 @@
         <v>49524230</v>
       </c>
       <c r="AZ179" s="10" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="180">
@@ -38963,22 +38975,22 @@
         <v>169</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="D180" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>194</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="H180" s="3" t="s">
         <v>222</v>
@@ -39008,13 +39020,13 @@
         <v>278</v>
       </c>
       <c r="Q180" s="3" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="R180" s="10" t="s">
         <v>1193</v>
       </c>
       <c r="S180" s="3" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="T180" s="3" t="s">
         <v>230</v>
@@ -39038,10 +39050,10 @@
         <v>233</v>
       </c>
       <c r="AA180" s="10" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="AB180" s="3" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="AC180" s="3" t="s">
         <v>225</v>
@@ -39050,7 +39062,7 @@
         <v>87500</v>
       </c>
       <c r="AE180" s="3" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="AF180" s="3" t="s">
         <v>225</v>
@@ -39119,22 +39131,22 @@
         <v>169</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="D181" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>194</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="H181" s="3" t="s">
         <v>222</v>
@@ -39164,13 +39176,13 @@
         <v>278</v>
       </c>
       <c r="Q181" s="3" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="R181" s="10" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="S181" s="3" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="T181" s="3" t="s">
         <v>230</v>
@@ -39182,10 +39194,10 @@
         <v>225</v>
       </c>
       <c r="W181" s="3" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="X181" s="10" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="Y181" s="10" t="s">
         <v>233</v>
@@ -39197,7 +39209,7 @@
         <v>1044</v>
       </c>
       <c r="AB181" s="3" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="AC181" s="3" t="s">
         <v>225</v>
@@ -39206,7 +39218,7 @@
         <v>25000</v>
       </c>
       <c r="AE181" s="3" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="AF181" s="3" t="s">
         <v>225</v>
@@ -39227,7 +39239,7 @@
         <v>239</v>
       </c>
       <c r="AL181" s="3" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="AM181" s="10" t="n">
         <v>260809000</v>
@@ -39277,22 +39289,22 @@
         <v>169</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="D182" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>194</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="H182" s="3" t="s">
         <v>222</v>
@@ -39322,13 +39334,13 @@
         <v>278</v>
       </c>
       <c r="Q182" s="3" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="R182" s="10" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="S182" s="3" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="T182" s="3" t="s">
         <v>230</v>
@@ -39343,19 +39355,19 @@
         <v>231</v>
       </c>
       <c r="X182" s="10" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="Y182" s="10" t="s">
         <v>233</v>
       </c>
       <c r="Z182" s="10" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="AA182" s="10" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="AB182" s="3" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="AC182" s="3" t="s">
         <v>225</v>
@@ -39364,7 +39376,7 @@
         <v>174866</v>
       </c>
       <c r="AE182" s="3" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="AF182" s="3" t="s">
         <v>225</v>
@@ -39435,22 +39447,22 @@
         <v>169</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="D183" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>194</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="H183" s="3" t="s">
         <v>222</v>
@@ -39480,13 +39492,13 @@
         <v>278</v>
       </c>
       <c r="Q183" s="3" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="R183" s="10" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="S183" s="3" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="T183" s="3" t="s">
         <v>230</v>
@@ -39513,7 +39525,7 @@
         <v>248</v>
       </c>
       <c r="AB183" s="3" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="AC183" s="3" t="s">
         <v>225</v>
@@ -39522,7 +39534,7 @@
         <v>0</v>
       </c>
       <c r="AE183" s="3" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="AF183" s="3" t="s">
         <v>230</v>
@@ -39593,22 +39605,22 @@
         <v>169</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="D184" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>194</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="H184" s="3" t="s">
         <v>222</v>
@@ -39638,13 +39650,13 @@
         <v>278</v>
       </c>
       <c r="Q184" s="3" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="R184" s="10" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="S184" s="3" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="T184" s="3" t="s">
         <v>230</v>
@@ -39656,22 +39668,22 @@
         <v>225</v>
       </c>
       <c r="W184" s="3" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="X184" s="10" t="s">
         <v>222</v>
       </c>
       <c r="Y184" s="10" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="Z184" s="10" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="AA184" s="10" t="s">
         <v>248</v>
       </c>
       <c r="AB184" s="3" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="AC184" s="3" t="s">
         <v>225</v>
@@ -39680,7 +39692,7 @@
         <v>47500</v>
       </c>
       <c r="AE184" s="3" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="AF184" s="3" t="s">
         <v>225</v>
@@ -39743,7 +39755,7 @@
         <v>-264340000</v>
       </c>
       <c r="AZ184" s="10" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="185">
@@ -39751,22 +39763,22 @@
         <v>169</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="D185" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>194</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="H185" s="3" t="s">
         <v>222</v>
@@ -39796,13 +39808,13 @@
         <v>278</v>
       </c>
       <c r="Q185" s="3" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="R185" s="10" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="S185" s="3" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="T185" s="3" t="s">
         <v>230</v>
@@ -39826,10 +39838,10 @@
         <v>222</v>
       </c>
       <c r="AA185" s="10" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="AB185" s="3" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="AC185" s="3" t="s">
         <v>225</v>
@@ -39838,7 +39850,7 @@
         <v>24999.96</v>
       </c>
       <c r="AE185" s="3" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="AF185" s="3" t="s">
         <v>225</v>
@@ -39907,20 +39919,20 @@
         <v>169</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="C186" s="3"/>
       <c r="D186" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>194</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="H186" s="3" t="s">
         <v>222</v>
@@ -39950,13 +39962,13 @@
         <v>278</v>
       </c>
       <c r="Q186" s="3" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="R186" s="10" t="s">
         <v>511</v>
       </c>
       <c r="S186" s="3" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="T186" s="3" t="s">
         <v>230</v>
@@ -39983,7 +39995,7 @@
         <v>511</v>
       </c>
       <c r="AB186" s="3" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="AC186" s="3" t="s">
         <v>225</v>
@@ -39992,7 +40004,7 @@
         <v>117500</v>
       </c>
       <c r="AE186" s="3" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="AF186" s="3" t="s">
         <v>225</v>
@@ -40063,22 +40075,22 @@
         <v>169</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="D187" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>195</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H187" s="3" t="s">
         <v>222</v>
@@ -40108,13 +40120,13 @@
         <v>278</v>
       </c>
       <c r="Q187" s="3" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="R187" s="10" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="S187" s="3" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="T187" s="3" t="s">
         <v>225</v>
@@ -40138,10 +40150,10 @@
         <v>222</v>
       </c>
       <c r="AA187" s="10" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="AB187" s="3" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="AC187" s="3" t="s">
         <v>225</v>
@@ -40213,7 +40225,7 @@
         <v>0</v>
       </c>
       <c r="AZ187" s="10" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="188">
@@ -40221,22 +40233,22 @@
         <v>169</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="D188" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>195</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H188" s="3" t="s">
         <v>222</v>
@@ -40266,13 +40278,13 @@
         <v>278</v>
       </c>
       <c r="Q188" s="3" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="R188" s="10" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="S188" s="3" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="T188" s="3" t="s">
         <v>230</v>
@@ -40296,10 +40308,10 @@
         <v>222</v>
       </c>
       <c r="AA188" s="10" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="AB188" s="3" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="AC188" s="3" t="s">
         <v>225</v>
@@ -40308,7 +40320,7 @@
         <v>0</v>
       </c>
       <c r="AE188" s="3" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="AF188" s="3" t="s">
         <v>230</v>
@@ -40371,7 +40383,7 @@
         <v>0</v>
       </c>
       <c r="AZ188" s="10" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="189">
@@ -40379,22 +40391,22 @@
         <v>169</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="D189" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>195</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H189" s="3" t="s">
         <v>222</v>
@@ -40424,13 +40436,13 @@
         <v>278</v>
       </c>
       <c r="Q189" s="3" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="R189" s="10" t="s">
         <v>314</v>
       </c>
       <c r="S189" s="3" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="T189" s="3" t="s">
         <v>230</v>
@@ -40454,10 +40466,10 @@
         <v>358</v>
       </c>
       <c r="AA189" s="10" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="AB189" s="3" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="AC189" s="3" t="s">
         <v>225</v>
@@ -40466,7 +40478,7 @@
         <v>0</v>
       </c>
       <c r="AE189" s="3" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="AF189" s="3" t="s">
         <v>230</v>
@@ -40529,7 +40541,7 @@
         <v>0</v>
       </c>
       <c r="AZ189" s="10" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="190">
@@ -40540,19 +40552,19 @@
         <v>1063</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="D190" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>195</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H190" s="3" t="s">
         <v>222</v>
@@ -40582,13 +40594,13 @@
         <v>226</v>
       </c>
       <c r="Q190" s="3" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="R190" s="10" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="S190" s="3" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="T190" s="3" t="s">
         <v>230</v>
@@ -40615,7 +40627,7 @@
         <v>248</v>
       </c>
       <c r="AB190" s="3" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="AC190" s="3" t="s">
         <v>225</v>
@@ -40624,7 +40636,7 @@
         <v>54000</v>
       </c>
       <c r="AE190" s="3" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="AF190" s="3" t="s">
         <v>225</v>
@@ -40687,7 +40699,7 @@
         <v>43228852</v>
       </c>
       <c r="AZ190" s="10" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="191">
@@ -40695,22 +40707,22 @@
         <v>169</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="D191" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>195</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H191" s="3" t="s">
         <v>222</v>
@@ -40740,13 +40752,13 @@
         <v>226</v>
       </c>
       <c r="Q191" s="3" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="R191" s="10" t="s">
         <v>1419</v>
       </c>
       <c r="S191" s="3" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="T191" s="3" t="s">
         <v>230</v>
@@ -40770,10 +40782,10 @@
         <v>232</v>
       </c>
       <c r="AA191" s="10" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="AB191" s="3" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="AC191" s="3" t="s">
         <v>225</v>
@@ -40782,7 +40794,7 @@
         <v>42500</v>
       </c>
       <c r="AE191" s="3" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="AF191" s="3" t="s">
         <v>225</v>
@@ -40845,7 +40857,7 @@
         <v>210553730</v>
       </c>
       <c r="AZ191" s="10" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="192">
@@ -40853,22 +40865,22 @@
         <v>169</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="D192" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>195</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H192" s="3" t="s">
         <v>222</v>
@@ -40898,13 +40910,13 @@
         <v>278</v>
       </c>
       <c r="Q192" s="3" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="R192" s="10" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="S192" s="3" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="T192" s="3" t="s">
         <v>225</v>
@@ -40919,7 +40931,7 @@
         <v>222</v>
       </c>
       <c r="X192" s="10" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="Y192" s="10" t="s">
         <v>232</v>
@@ -40931,7 +40943,7 @@
         <v>248</v>
       </c>
       <c r="AB192" s="3" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="AC192" s="3" t="s">
         <v>225</v>
@@ -40940,7 +40952,7 @@
         <v>29700</v>
       </c>
       <c r="AE192" s="3" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AF192" s="3" t="s">
         <v>225</v>
@@ -41009,22 +41021,22 @@
         <v>169</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="D193" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>195</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H193" s="3" t="s">
         <v>222</v>
@@ -41054,13 +41066,13 @@
         <v>226</v>
       </c>
       <c r="Q193" s="3" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="R193" s="10" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="S193" s="3" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="T193" s="3" t="s">
         <v>230</v>
@@ -41075,26 +41087,26 @@
         <v>222</v>
       </c>
       <c r="X193" s="10" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="Y193" s="10" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="Z193" s="10" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="AA193" s="10" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="AB193" s="3" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="AC193" s="3" t="s">
         <v>225</v>
       </c>
       <c r="AD193" s="10"/>
       <c r="AE193" s="3" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="AF193" s="3" t="s">
         <v>225</v>
@@ -41157,7 +41169,7 @@
         <v>75010000</v>
       </c>
       <c r="AZ193" s="10" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="194">
@@ -41165,22 +41177,22 @@
         <v>169</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="D194" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>195</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H194" s="3" t="s">
         <v>222</v>
@@ -41210,13 +41222,13 @@
         <v>278</v>
       </c>
       <c r="Q194" s="3" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="R194" s="10" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="S194" s="3" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="T194" s="3" t="s">
         <v>230</v>
@@ -41243,7 +41255,7 @@
         <v>222</v>
       </c>
       <c r="AB194" s="3" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="AC194" s="3" t="s">
         <v>225</v>
@@ -41315,7 +41327,7 @@
         <v>1207993.64</v>
       </c>
       <c r="AZ194" s="10" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="195">
@@ -41323,22 +41335,22 @@
         <v>169</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="D195" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>195</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H195" s="3" t="s">
         <v>222</v>
@@ -41368,13 +41380,13 @@
         <v>278</v>
       </c>
       <c r="Q195" s="3" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="R195" s="10" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="S195" s="3" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="T195" s="3" t="s">
         <v>230</v>
@@ -41398,10 +41410,10 @@
         <v>222</v>
       </c>
       <c r="AA195" s="10" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="AB195" s="3" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="AC195" s="3" t="s">
         <v>225</v>
@@ -41410,7 +41422,7 @@
         <v>40000</v>
       </c>
       <c r="AE195" s="3" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="AF195" s="3" t="s">
         <v>230</v>
@@ -41481,22 +41493,22 @@
         <v>169</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D196" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>195</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H196" s="3" t="s">
         <v>222</v>
@@ -41526,13 +41538,13 @@
         <v>278</v>
       </c>
       <c r="Q196" s="3" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="R196" s="10" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="S196" s="3" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="T196" s="3" t="s">
         <v>230</v>
@@ -41559,7 +41571,7 @@
         <v>222</v>
       </c>
       <c r="AB196" s="3" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="AC196" s="3" t="s">
         <v>225</v>
@@ -41568,7 +41580,7 @@
         <v>16500</v>
       </c>
       <c r="AE196" s="3" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="AF196" s="3" t="s">
         <v>230</v>
@@ -41631,7 +41643,7 @@
         <v>379861</v>
       </c>
       <c r="AZ196" s="10" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="197">
@@ -41639,25 +41651,25 @@
         <v>169</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D197" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>195</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H197" s="3" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="I197" s="3" t="s">
         <v>175</v>
@@ -41684,10 +41696,10 @@
         <v>278</v>
       </c>
       <c r="Q197" s="3" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="R197" s="10" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="S197" s="3" t="s">
         <v>222</v>
@@ -41702,7 +41714,7 @@
         <v>225</v>
       </c>
       <c r="W197" s="3" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="X197" s="10" t="s">
         <v>222</v>
@@ -41714,7 +41726,7 @@
         <v>316</v>
       </c>
       <c r="AA197" s="10" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="AB197" s="3" t="s">
         <v>222</v>
@@ -41726,7 +41738,7 @@
         <v>0</v>
       </c>
       <c r="AE197" s="3" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="AF197" s="3" t="s">
         <v>225</v>
@@ -41747,7 +41759,7 @@
         <v>1113</v>
       </c>
       <c r="AL197" s="3" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="AM197" s="10" t="n">
         <v>724912000</v>
@@ -41797,22 +41809,22 @@
         <v>169</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="D198" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>195</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H198" s="3" t="s">
         <v>222</v>
@@ -41842,13 +41854,13 @@
         <v>278</v>
       </c>
       <c r="Q198" s="3" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="R198" s="10" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="S198" s="3" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="T198" s="3" t="s">
         <v>230</v>
@@ -41884,7 +41896,7 @@
         <v>0</v>
       </c>
       <c r="AE198" s="3" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="AF198" s="3" t="s">
         <v>225</v>
@@ -41947,7 +41959,7 @@
         <v>12733526.36</v>
       </c>
       <c r="AZ198" s="10" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="199">
@@ -41955,25 +41967,25 @@
         <v>169</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="D199" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>195</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="I199" s="3" t="s">
         <v>176</v>
@@ -42000,13 +42012,13 @@
         <v>226</v>
       </c>
       <c r="Q199" s="3" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="R199" s="10" t="s">
         <v>906</v>
       </c>
       <c r="S199" s="3" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="T199" s="3" t="s">
         <v>225</v>
@@ -42105,7 +42117,7 @@
         <v>0</v>
       </c>
       <c r="AZ199" s="10" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="200">
@@ -42113,22 +42125,22 @@
         <v>169</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="D200" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>195</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H200" s="3" t="s">
         <v>222</v>
@@ -42158,13 +42170,13 @@
         <v>226</v>
       </c>
       <c r="Q200" s="3" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="R200" s="10" t="s">
         <v>357</v>
       </c>
       <c r="S200" s="3" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="T200" s="3" t="s">
         <v>230</v>
@@ -42191,7 +42203,7 @@
         <v>222</v>
       </c>
       <c r="AB200" s="3" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="AC200" s="3" t="s">
         <v>225</v>
@@ -42200,7 +42212,7 @@
         <v>10500</v>
       </c>
       <c r="AE200" s="3" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="AF200" s="3" t="s">
         <v>230</v>
@@ -42263,7 +42275,7 @@
         <v>247430</v>
       </c>
       <c r="AZ200" s="10" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="201">
@@ -42271,22 +42283,22 @@
         <v>169</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="D201" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>195</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H201" s="3" t="s">
         <v>222</v>
@@ -42316,13 +42328,13 @@
         <v>278</v>
       </c>
       <c r="Q201" s="3" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="R201" s="10" t="s">
         <v>927</v>
       </c>
       <c r="S201" s="3" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="T201" s="3" t="s">
         <v>230</v>
@@ -42346,10 +42358,10 @@
         <v>232</v>
       </c>
       <c r="AA201" s="10" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="AB201" s="3" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="AC201" s="3" t="s">
         <v>225</v>
@@ -42358,7 +42370,7 @@
         <v>54963</v>
       </c>
       <c r="AE201" s="3" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="AF201" s="3" t="s">
         <v>225</v>
@@ -42421,7 +42433,7 @@
         <v>1791465.66</v>
       </c>
       <c r="AZ201" s="10" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="202">
@@ -42429,22 +42441,22 @@
         <v>169</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="D202" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>195</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H202" s="3" t="s">
         <v>222</v>
@@ -42474,13 +42486,13 @@
         <v>278</v>
       </c>
       <c r="Q202" s="3" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="R202" s="10" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="S202" s="3" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="T202" s="3" t="s">
         <v>230</v>
@@ -42507,7 +42519,7 @@
         <v>222</v>
       </c>
       <c r="AB202" s="3" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="AC202" s="3" t="s">
         <v>225</v>
@@ -42587,22 +42599,22 @@
         <v>169</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="D203" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>197</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="H203" s="3" t="s">
         <v>222</v>
@@ -42632,13 +42644,13 @@
         <v>291</v>
       </c>
       <c r="Q203" s="3" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="R203" s="10" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="S203" s="3" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="T203" s="3" t="s">
         <v>230</v>
@@ -42665,7 +42677,7 @@
         <v>248</v>
       </c>
       <c r="AB203" s="3" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="AC203" s="3" t="s">
         <v>230</v>
@@ -42674,7 +42686,7 @@
         <v>0</v>
       </c>
       <c r="AE203" s="3" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="AF203" s="3" t="s">
         <v>225</v>
@@ -42737,7 +42749,7 @@
         <v>371455</v>
       </c>
       <c r="AZ203" s="10" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="204">
@@ -42745,22 +42757,22 @@
         <v>169</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="D204" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>197</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="H204" s="3" t="s">
         <v>222</v>
@@ -42790,13 +42802,13 @@
         <v>385</v>
       </c>
       <c r="Q204" s="3" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="R204" s="10" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="S204" s="3" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="T204" s="3" t="s">
         <v>230</v>
@@ -42823,7 +42835,7 @@
         <v>245</v>
       </c>
       <c r="AB204" s="3" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="AC204" s="3" t="s">
         <v>230</v>
@@ -42832,7 +42844,7 @@
         <v>0</v>
       </c>
       <c r="AE204" s="3" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="AF204" s="3" t="s">
         <v>225</v>
@@ -42901,25 +42913,25 @@
         <v>169</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="D205" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>197</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="I205" s="3" t="s">
         <v>175</v>
@@ -42946,13 +42958,13 @@
         <v>226</v>
       </c>
       <c r="Q205" s="3" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="R205" s="10" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="S205" s="3" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="T205" s="3" t="s">
         <v>230</v>
@@ -42976,7 +42988,7 @@
         <v>234</v>
       </c>
       <c r="AA205" s="10" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="AB205" s="3" t="s">
         <v>1343</v>
@@ -42988,7 +43000,7 @@
         <v>57500</v>
       </c>
       <c r="AE205" s="3" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="AF205" s="3" t="s">
         <v>225</v>
@@ -43051,7 +43063,7 @@
         <v>480953000</v>
       </c>
       <c r="AZ205" s="10" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="206">
@@ -43059,22 +43071,22 @@
         <v>169</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="D206" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>197</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="H206" s="3" t="s">
         <v>222</v>
@@ -43104,13 +43116,13 @@
         <v>291</v>
       </c>
       <c r="Q206" s="3" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="R206" s="10" t="s">
         <v>1083</v>
       </c>
       <c r="S206" s="3" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="T206" s="3" t="s">
         <v>230</v>
@@ -43134,10 +43146,10 @@
         <v>247</v>
       </c>
       <c r="AA206" s="10" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="AB206" s="3" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="AC206" s="3" t="s">
         <v>225</v>
@@ -43146,7 +43158,7 @@
         <v>95000</v>
       </c>
       <c r="AE206" s="3" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="AF206" s="3" t="s">
         <v>225</v>
@@ -43209,7 +43221,7 @@
         <v>2623876398</v>
       </c>
       <c r="AZ206" s="10" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="207">
@@ -43217,22 +43229,22 @@
         <v>169</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="D207" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>197</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="H207" s="3" t="s">
         <v>222</v>
@@ -43244,7 +43256,7 @@
         <v>300</v>
       </c>
       <c r="K207" s="3" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="L207" s="3" t="s">
         <v>230</v>
@@ -43262,13 +43274,13 @@
         <v>291</v>
       </c>
       <c r="Q207" s="3" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="R207" s="10" t="s">
         <v>906</v>
       </c>
       <c r="S207" s="3" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="T207" s="3" t="s">
         <v>230</v>
@@ -43283,7 +43295,7 @@
         <v>222</v>
       </c>
       <c r="X207" s="10" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="Y207" s="10" t="s">
         <v>222</v>
@@ -43292,7 +43304,7 @@
         <v>222</v>
       </c>
       <c r="AA207" s="10" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="AB207" s="3" t="s">
         <v>222</v>
@@ -43304,7 +43316,7 @@
         <v>0</v>
       </c>
       <c r="AE207" s="3" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="AF207" s="3" t="s">
         <v>225</v>
@@ -43367,7 +43379,7 @@
         <v>33489000</v>
       </c>
       <c r="AZ207" s="10" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="208">
@@ -43375,25 +43387,25 @@
         <v>169</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="D208" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>197</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="H208" s="3" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="I208" s="3" t="s">
         <v>174</v>
@@ -43420,13 +43432,13 @@
         <v>226</v>
       </c>
       <c r="Q208" s="3" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="R208" s="10" t="s">
         <v>1408</v>
       </c>
       <c r="S208" s="3" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="T208" s="3" t="s">
         <v>230</v>
@@ -43444,16 +43456,16 @@
         <v>316</v>
       </c>
       <c r="Y208" s="10" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="Z208" s="10" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="AA208" s="10" t="s">
         <v>248</v>
       </c>
       <c r="AB208" s="3" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="AC208" s="3" t="s">
         <v>225</v>
@@ -43462,7 +43474,7 @@
         <v>0</v>
       </c>
       <c r="AE208" s="3" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="AF208" s="3" t="s">
         <v>225</v>
@@ -43533,22 +43545,22 @@
         <v>169</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="D209" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>197</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="H209" s="3" t="s">
         <v>222</v>
@@ -43578,13 +43590,13 @@
         <v>291</v>
       </c>
       <c r="Q209" s="3" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="R209" s="10" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="S209" s="3" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="T209" s="3" t="s">
         <v>225</v>
@@ -43608,10 +43620,10 @@
         <v>232</v>
       </c>
       <c r="AA209" s="10" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="AB209" s="3" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="AC209" s="3" t="s">
         <v>225</v>
@@ -43620,7 +43632,7 @@
         <v>22500</v>
       </c>
       <c r="AE209" s="3" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="AF209" s="3" t="s">
         <v>225</v>
@@ -43641,7 +43653,7 @@
         <v>222</v>
       </c>
       <c r="AL209" s="3" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="AM209" s="10" t="n">
         <v>58011132</v>
@@ -43683,7 +43695,7 @@
         <v>66897251</v>
       </c>
       <c r="AZ209" s="10" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="210">
@@ -43691,22 +43703,22 @@
         <v>169</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="D210" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>197</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="H210" s="3" t="s">
         <v>222</v>
@@ -43718,7 +43730,7 @@
         <v>223</v>
       </c>
       <c r="K210" s="3" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="L210" s="3" t="s">
         <v>230</v>
@@ -43736,13 +43748,13 @@
         <v>571</v>
       </c>
       <c r="Q210" s="3" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="R210" s="10" t="s">
         <v>228</v>
       </c>
       <c r="S210" s="3" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="T210" s="3" t="s">
         <v>230</v>
@@ -43760,7 +43772,7 @@
         <v>222</v>
       </c>
       <c r="Y210" s="10" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="Z210" s="10" t="s">
         <v>368</v>
@@ -43769,7 +43781,7 @@
         <v>248</v>
       </c>
       <c r="AB210" s="3" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="AC210" s="3" t="s">
         <v>222</v>
@@ -43778,7 +43790,7 @@
         <v>0</v>
       </c>
       <c r="AE210" s="3" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="AF210" s="3" t="s">
         <v>225</v>
@@ -43799,7 +43811,7 @@
         <v>398</v>
       </c>
       <c r="AL210" s="3" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AM210" s="10" t="n">
         <v>0</v>
@@ -43841,7 +43853,7 @@
         <v>-15059590.41</v>
       </c>
       <c r="AZ210" s="10" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="211">
@@ -43849,22 +43861,22 @@
         <v>169</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="D211" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>197</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="H211" s="3" t="s">
         <v>222</v>
@@ -43894,13 +43906,13 @@
         <v>291</v>
       </c>
       <c r="Q211" s="3" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="R211" s="10" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="S211" s="3" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="T211" s="3" t="s">
         <v>230</v>
@@ -43915,7 +43927,7 @@
         <v>231</v>
       </c>
       <c r="X211" s="10" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Y211" s="10" t="s">
         <v>233</v>
@@ -43927,7 +43939,7 @@
         <v>248</v>
       </c>
       <c r="AB211" s="3" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="AC211" s="3" t="s">
         <v>225</v>
@@ -43936,7 +43948,7 @@
         <v>65000</v>
       </c>
       <c r="AE211" s="3" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="AF211" s="3" t="s">
         <v>225</v>
@@ -43999,7 +44011,7 @@
         <v>12441000</v>
       </c>
       <c r="AZ211" s="10" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="212">
@@ -44007,22 +44019,22 @@
         <v>169</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="D212" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>197</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="H212" s="3" t="s">
         <v>222</v>
@@ -44058,7 +44070,7 @@
         <v>822</v>
       </c>
       <c r="S212" s="3" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="T212" s="3" t="s">
         <v>230</v>
@@ -44073,19 +44085,19 @@
         <v>222</v>
       </c>
       <c r="X212" s="10" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="Y212" s="10" t="s">
         <v>222</v>
       </c>
       <c r="Z212" s="10" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="AA212" s="10" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="AB212" s="3" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="AC212" s="3" t="s">
         <v>222</v>
@@ -44163,22 +44175,22 @@
         <v>169</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="D213" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>197</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="H213" s="3" t="s">
         <v>222</v>
@@ -44208,13 +44220,13 @@
         <v>291</v>
       </c>
       <c r="Q213" s="3" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="R213" s="10" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="S213" s="3" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="T213" s="3" t="s">
         <v>225</v>
@@ -44241,7 +44253,7 @@
         <v>368</v>
       </c>
       <c r="AB213" s="3" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="AC213" s="3" t="s">
         <v>225</v>
@@ -44250,7 +44262,7 @@
         <v>8839</v>
       </c>
       <c r="AE213" s="3" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="AF213" s="3" t="s">
         <v>225</v>
@@ -44319,22 +44331,22 @@
         <v>169</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="D214" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="H214" s="3" t="s">
         <v>222</v>
@@ -44364,13 +44376,13 @@
         <v>571</v>
       </c>
       <c r="Q214" s="3" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="R214" s="10" t="s">
         <v>1052</v>
       </c>
       <c r="S214" s="3" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="T214" s="3" t="s">
         <v>225</v>
@@ -44397,7 +44409,7 @@
         <v>222</v>
       </c>
       <c r="AB214" s="3" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="AC214" s="3" t="s">
         <v>225</v>
@@ -44406,7 +44418,7 @@
         <v>0</v>
       </c>
       <c r="AE214" s="3" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="AF214" s="3" t="s">
         <v>230</v>
@@ -44477,22 +44489,22 @@
         <v>169</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="D215" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="H215" s="3" t="s">
         <v>222</v>
@@ -44504,7 +44516,7 @@
         <v>300</v>
       </c>
       <c r="K215" s="3" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="L215" s="3" t="s">
         <v>230</v>
@@ -44522,13 +44534,13 @@
         <v>278</v>
       </c>
       <c r="Q215" s="3" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="R215" s="10" t="s">
         <v>325</v>
       </c>
       <c r="S215" s="3" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="T215" s="3" t="s">
         <v>225</v>
@@ -44555,7 +44567,7 @@
         <v>234</v>
       </c>
       <c r="AB215" s="3" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="AC215" s="3" t="s">
         <v>230</v>
@@ -44564,7 +44576,7 @@
         <v>0</v>
       </c>
       <c r="AE215" s="3" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="AF215" s="3" t="s">
         <v>225</v>
@@ -44627,7 +44639,7 @@
         <v>34458210</v>
       </c>
       <c r="AZ215" s="10" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="216">
@@ -44635,22 +44647,22 @@
         <v>169</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="D216" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="H216" s="3" t="s">
         <v>222</v>
@@ -44680,13 +44692,13 @@
         <v>571</v>
       </c>
       <c r="Q216" s="3" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="R216" s="10" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="S216" s="3" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="T216" s="3" t="s">
         <v>230</v>
@@ -44710,10 +44722,10 @@
         <v>222</v>
       </c>
       <c r="AA216" s="10" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="AB216" s="3" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="AC216" s="3" t="s">
         <v>225</v>
@@ -44722,7 +44734,7 @@
         <v>12250</v>
       </c>
       <c r="AE216" s="3" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="AF216" s="3" t="s">
         <v>230</v>
@@ -44785,7 +44797,7 @@
         <v>0</v>
       </c>
       <c r="AZ216" s="10" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="217">
@@ -44793,22 +44805,22 @@
         <v>169</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="D217" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="H217" s="3" t="s">
         <v>222</v>
@@ -44820,7 +44832,7 @@
         <v>300</v>
       </c>
       <c r="K217" s="3" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="L217" s="3" t="s">
         <v>230</v>
@@ -44835,16 +44847,16 @@
         <v>222</v>
       </c>
       <c r="P217" s="3" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="Q217" s="3" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="R217" s="10" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="S217" s="3" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="T217" s="3" t="s">
         <v>230</v>
@@ -44868,10 +44880,10 @@
         <v>232</v>
       </c>
       <c r="AA217" s="10" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="AB217" s="3" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="AC217" s="3" t="s">
         <v>225</v>
@@ -44880,7 +44892,7 @@
         <v>150000</v>
       </c>
       <c r="AE217" s="3" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="AF217" s="3" t="s">
         <v>225</v>
@@ -44949,25 +44961,25 @@
         <v>169</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="D218" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="H218" s="3" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="I218" s="3" t="s">
         <v>173</v>
@@ -44976,7 +44988,7 @@
         <v>223</v>
       </c>
       <c r="K218" s="3" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="L218" s="3" t="s">
         <v>230</v>
@@ -44994,13 +45006,13 @@
         <v>278</v>
       </c>
       <c r="Q218" s="3" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="R218" s="10" t="s">
         <v>280</v>
       </c>
       <c r="S218" s="3" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="T218" s="3" t="s">
         <v>230</v>
@@ -45015,7 +45027,7 @@
         <v>222</v>
       </c>
       <c r="X218" s="10" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="Y218" s="10" t="s">
         <v>233</v>
@@ -45024,10 +45036,10 @@
         <v>232</v>
       </c>
       <c r="AA218" s="10" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="AB218" s="3" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="AC218" s="3" t="s">
         <v>225</v>
@@ -45036,7 +45048,7 @@
         <v>150000</v>
       </c>
       <c r="AE218" s="3" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="AF218" s="3" t="s">
         <v>225</v>
@@ -45057,7 +45069,7 @@
         <v>398</v>
       </c>
       <c r="AL218" s="3" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="AM218" s="10" t="n">
         <v>1363000000</v>
@@ -45099,7 +45111,7 @@
         <v>1367880100.66</v>
       </c>
       <c r="AZ218" s="10" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="219">
@@ -45107,22 +45119,22 @@
         <v>169</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="D219" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="H219" s="3" t="s">
         <v>222</v>
@@ -45152,13 +45164,13 @@
         <v>278</v>
       </c>
       <c r="Q219" s="3" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="R219" s="10" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="S219" s="3" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="T219" s="3" t="s">
         <v>230</v>
@@ -45182,10 +45194,10 @@
         <v>232</v>
       </c>
       <c r="AA219" s="10" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="AB219" s="3" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="AC219" s="3" t="s">
         <v>225</v>
@@ -45194,7 +45206,7 @@
         <v>27500</v>
       </c>
       <c r="AE219" s="3" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="AF219" s="3" t="s">
         <v>225</v>
@@ -45257,7 +45269,7 @@
         <v>51909519.79</v>
       </c>
       <c r="AZ219" s="10" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="220">
@@ -45265,22 +45277,22 @@
         <v>169</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="D220" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="H220" s="3" t="s">
         <v>222</v>
@@ -45310,13 +45322,13 @@
         <v>278</v>
       </c>
       <c r="Q220" s="3" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="R220" s="10" t="s">
         <v>1419</v>
       </c>
       <c r="S220" s="3" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="T220" s="3" t="s">
         <v>230</v>
@@ -45343,7 +45355,7 @@
         <v>222</v>
       </c>
       <c r="AB220" s="3" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="AC220" s="3" t="s">
         <v>225</v>
@@ -45352,7 +45364,7 @@
         <v>0</v>
       </c>
       <c r="AE220" s="3" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="AF220" s="3" t="s">
         <v>230</v>
@@ -45415,7 +45427,7 @@
         <v>0</v>
       </c>
       <c r="AZ220" s="10" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="221">
@@ -45423,22 +45435,22 @@
         <v>169</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="D221" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="H221" s="3" t="s">
         <v>222</v>
@@ -45450,7 +45462,7 @@
         <v>300</v>
       </c>
       <c r="K221" s="3" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="L221" s="3" t="s">
         <v>230</v>
@@ -45468,13 +45480,13 @@
         <v>278</v>
       </c>
       <c r="Q221" s="3" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="R221" s="10" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="S221" s="3" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="T221" s="3" t="s">
         <v>230</v>
@@ -45498,10 +45510,10 @@
         <v>222</v>
       </c>
       <c r="AA221" s="10" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="AB221" s="3" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="AC221" s="3" t="s">
         <v>225</v>
@@ -45510,7 +45522,7 @@
         <v>0</v>
       </c>
       <c r="AE221" s="3" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="AF221" s="3" t="s">
         <v>225</v>
@@ -45531,7 +45543,7 @@
         <v>398</v>
       </c>
       <c r="AL221" s="3" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="AM221" s="10" t="n">
         <v>7181000</v>
@@ -45573,7 +45585,7 @@
         <v>7519000</v>
       </c>
       <c r="AZ221" s="10" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="222">
@@ -45581,22 +45593,22 @@
         <v>169</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="D222" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="H222" s="3" t="s">
         <v>222</v>
@@ -45608,7 +45620,7 @@
         <v>300</v>
       </c>
       <c r="K222" s="3" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="L222" s="3" t="s">
         <v>230</v>
@@ -45626,13 +45638,13 @@
         <v>571</v>
       </c>
       <c r="Q222" s="3" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="R222" s="10" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="S222" s="3" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="T222" s="3" t="s">
         <v>230</v>
@@ -45644,7 +45656,7 @@
         <v>225</v>
       </c>
       <c r="W222" s="3" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="X222" s="10" t="s">
         <v>232</v>
@@ -45659,7 +45671,7 @@
         <v>248</v>
       </c>
       <c r="AB222" s="3" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="AC222" s="3" t="s">
         <v>230</v>
@@ -45668,7 +45680,7 @@
         <v>0</v>
       </c>
       <c r="AE222" s="3" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="AF222" s="3" t="s">
         <v>225</v>
@@ -45689,7 +45701,7 @@
         <v>398</v>
       </c>
       <c r="AL222" s="3" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="AM222" s="10" t="n">
         <v>6331000</v>
@@ -45731,7 +45743,7 @@
         <v>6331000</v>
       </c>
       <c r="AZ222" s="10" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="223">
@@ -45739,22 +45751,22 @@
         <v>169</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="D223" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="H223" s="3" t="s">
         <v>222</v>
@@ -45784,13 +45796,13 @@
         <v>278</v>
       </c>
       <c r="Q223" s="3" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="R223" s="10" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="S223" s="3" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="T223" s="3" t="s">
         <v>230</v>
@@ -45817,7 +45829,7 @@
         <v>248</v>
       </c>
       <c r="AB223" s="3" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="AC223" s="3" t="s">
         <v>225</v>
@@ -45826,7 +45838,7 @@
         <v>15420</v>
       </c>
       <c r="AE223" s="3" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="AF223" s="3" t="s">
         <v>230</v>
@@ -45889,7 +45901,7 @@
         <v>0</v>
       </c>
       <c r="AZ223" s="10" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="224">
@@ -45897,22 +45909,22 @@
         <v>169</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="D224" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="H224" s="3" t="s">
         <v>222</v>
@@ -45924,7 +45936,7 @@
         <v>300</v>
       </c>
       <c r="K224" s="3" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="L224" s="3" t="s">
         <v>230</v>
@@ -45942,13 +45954,13 @@
         <v>278</v>
       </c>
       <c r="Q224" s="3" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="R224" s="10" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="S224" s="3" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="T224" s="3" t="s">
         <v>230</v>
@@ -45975,7 +45987,7 @@
         <v>232</v>
       </c>
       <c r="AB224" s="3" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="AC224" s="3" t="s">
         <v>225</v>
@@ -45984,7 +45996,7 @@
         <v>0</v>
       </c>
       <c r="AE224" s="3" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="AF224" s="3" t="s">
         <v>225</v>
@@ -46005,7 +46017,7 @@
         <v>398</v>
       </c>
       <c r="AL224" s="3" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="AM224" s="10" t="n">
         <v>13391000</v>
@@ -46055,22 +46067,22 @@
         <v>169</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="D225" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="H225" s="3" t="s">
         <v>222</v>
@@ -46100,13 +46112,13 @@
         <v>278</v>
       </c>
       <c r="Q225" s="3" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="R225" s="10" t="s">
         <v>822</v>
       </c>
       <c r="S225" s="3" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="T225" s="3" t="s">
         <v>230</v>
@@ -46121,7 +46133,7 @@
         <v>222</v>
       </c>
       <c r="X225" s="10" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="Y225" s="10" t="s">
         <v>222</v>
@@ -46130,10 +46142,10 @@
         <v>222</v>
       </c>
       <c r="AA225" s="10" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="AB225" s="3" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="AC225" s="3" t="s">
         <v>225</v>
@@ -46142,7 +46154,7 @@
         <v>2800</v>
       </c>
       <c r="AE225" s="3" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="AF225" s="3" t="s">
         <v>230</v>
@@ -46211,22 +46223,22 @@
         <v>169</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="D226" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="H226" s="3" t="s">
         <v>222</v>
@@ -46256,13 +46268,13 @@
         <v>278</v>
       </c>
       <c r="Q226" s="3" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="R226" s="10" t="s">
         <v>325</v>
       </c>
       <c r="S226" s="3" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="T226" s="3" t="s">
         <v>230</v>
@@ -46283,13 +46295,13 @@
         <v>234</v>
       </c>
       <c r="Z226" s="10" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="AA226" s="10" t="s">
         <v>248</v>
       </c>
       <c r="AB226" s="3" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="AC226" s="3" t="s">
         <v>225</v>
@@ -46298,7 +46310,7 @@
         <v>100000</v>
       </c>
       <c r="AE226" s="3" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="AF226" s="3" t="s">
         <v>225</v>
@@ -46319,7 +46331,7 @@
         <v>563</v>
       </c>
       <c r="AL226" s="3" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="AM226" s="10" t="n">
         <v>282211663</v>
@@ -46361,7 +46373,7 @@
         <v>275454413</v>
       </c>
       <c r="AZ226" s="10" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="227">
@@ -46369,22 +46381,22 @@
         <v>169</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="D227" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="H227" s="3" t="s">
         <v>222</v>
@@ -46414,13 +46426,13 @@
         <v>278</v>
       </c>
       <c r="Q227" s="3" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="R227" s="10" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="S227" s="3" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="T227" s="3" t="s">
         <v>230</v>
@@ -46444,10 +46456,10 @@
         <v>232</v>
       </c>
       <c r="AA227" s="10" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="AB227" s="3" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="AC227" s="3" t="s">
         <v>225</v>
@@ -46456,7 +46468,7 @@
         <v>42000</v>
       </c>
       <c r="AE227" s="3" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="AF227" s="3" t="s">
         <v>225</v>
@@ -46527,22 +46539,22 @@
         <v>169</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="D228" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="H228" s="3" t="s">
         <v>222</v>
@@ -46554,7 +46566,7 @@
         <v>223</v>
       </c>
       <c r="K228" s="3" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="L228" s="3" t="s">
         <v>230</v>
@@ -46572,13 +46584,13 @@
         <v>571</v>
       </c>
       <c r="Q228" s="3" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="R228" s="10" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="S228" s="3" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="T228" s="3" t="s">
         <v>230</v>
@@ -46605,7 +46617,7 @@
         <v>1292</v>
       </c>
       <c r="AB228" s="3" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="AC228" s="3" t="s">
         <v>225</v>
@@ -46614,7 +46626,7 @@
         <v>28000</v>
       </c>
       <c r="AE228" s="3" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="AF228" s="3" t="s">
         <v>225</v>
@@ -46635,7 +46647,7 @@
         <v>398</v>
       </c>
       <c r="AL228" s="3" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="AM228" s="10" t="n">
         <v>0</v>
@@ -46677,7 +46689,7 @@
         <v>9928326</v>
       </c>
       <c r="AZ228" s="10" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="229">
@@ -46685,22 +46697,22 @@
         <v>169</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="D229" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="H229" s="3" t="s">
         <v>222</v>
@@ -46730,13 +46742,13 @@
         <v>278</v>
       </c>
       <c r="Q229" s="3" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="R229" s="10" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="S229" s="3" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="T229" s="3" t="s">
         <v>230</v>
@@ -46763,7 +46775,7 @@
         <v>248</v>
       </c>
       <c r="AB229" s="3" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="AC229" s="3" t="s">
         <v>225</v>
@@ -46772,7 +46784,7 @@
         <v>0</v>
       </c>
       <c r="AE229" s="3" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="AF229" s="3" t="s">
         <v>230</v>
@@ -46835,7 +46847,7 @@
         <v>23606.01</v>
       </c>
       <c r="AZ229" s="10" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="230">
@@ -46843,22 +46855,22 @@
         <v>169</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="D230" s="10" t="n">
         <v>44</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H230" s="3" t="s">
         <v>222</v>
@@ -46888,13 +46900,13 @@
         <v>226</v>
       </c>
       <c r="Q230" s="3" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="R230" s="10" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="S230" s="3" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="T230" s="3" t="s">
         <v>230</v>
@@ -46921,7 +46933,7 @@
         <v>222</v>
       </c>
       <c r="AB230" s="3" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="AC230" s="3" t="s">
         <v>230</v>
@@ -46930,7 +46942,7 @@
         <v>0</v>
       </c>
       <c r="AE230" s="3" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="AF230" s="3" t="s">
         <v>230</v>
@@ -46999,22 +47011,22 @@
         <v>169</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="D231" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H231" s="3" t="s">
         <v>222</v>
@@ -47044,13 +47056,13 @@
         <v>255</v>
       </c>
       <c r="Q231" s="3" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="R231" s="10" t="s">
         <v>474</v>
       </c>
       <c r="S231" s="3" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="T231" s="3" t="s">
         <v>225</v>
@@ -47077,7 +47089,7 @@
         <v>248</v>
       </c>
       <c r="AB231" s="3" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="AC231" s="3" t="s">
         <v>225</v>
@@ -47086,7 +47098,7 @@
         <v>60000</v>
       </c>
       <c r="AE231" s="3" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="AF231" s="3" t="s">
         <v>225</v>
@@ -47155,22 +47167,22 @@
         <v>169</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="D232" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H232" s="3" t="s">
         <v>222</v>
@@ -47200,13 +47212,13 @@
         <v>291</v>
       </c>
       <c r="Q232" s="3" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="R232" s="10" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="S232" s="3" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="T232" s="3" t="s">
         <v>225</v>
@@ -47230,10 +47242,10 @@
         <v>232</v>
       </c>
       <c r="AA232" s="10" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="AB232" s="3" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="AC232" s="3" t="s">
         <v>225</v>
@@ -47242,7 +47254,7 @@
         <v>32000</v>
       </c>
       <c r="AE232" s="3" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="AF232" s="3" t="s">
         <v>225</v>
@@ -47313,22 +47325,22 @@
         <v>169</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="D233" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H233" s="3" t="s">
         <v>222</v>
@@ -47358,13 +47370,13 @@
         <v>266</v>
       </c>
       <c r="Q233" s="3" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="R233" s="10" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="S233" s="3" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="T233" s="3" t="s">
         <v>230</v>
@@ -47376,7 +47388,7 @@
         <v>225</v>
       </c>
       <c r="W233" s="3" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="X233" s="10" t="s">
         <v>232</v>
@@ -47388,7 +47400,7 @@
         <v>232</v>
       </c>
       <c r="AA233" s="10" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="AB233" s="3" t="s">
         <v>222</v>
@@ -47400,7 +47412,7 @@
         <v>0</v>
       </c>
       <c r="AE233" s="3" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="AF233" s="3" t="s">
         <v>225</v>
@@ -47469,22 +47481,22 @@
         <v>169</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="D234" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H234" s="3" t="s">
         <v>222</v>
@@ -47514,13 +47526,13 @@
         <v>226</v>
       </c>
       <c r="Q234" s="3" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="R234" s="10" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="S234" s="3" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="T234" s="3" t="s">
         <v>225</v>
@@ -47547,7 +47559,7 @@
         <v>222</v>
       </c>
       <c r="AB234" s="3" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="AC234" s="3" t="s">
         <v>230</v>
@@ -47556,7 +47568,7 @@
         <v>0</v>
       </c>
       <c r="AE234" s="3" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="AF234" s="3" t="s">
         <v>230</v>
@@ -47619,7 +47631,7 @@
         <v>31350</v>
       </c>
       <c r="AZ234" s="10" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="235">
@@ -47627,22 +47639,22 @@
         <v>169</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="D235" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H235" s="3" t="s">
         <v>222</v>
@@ -47672,13 +47684,13 @@
         <v>226</v>
       </c>
       <c r="Q235" s="3" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="R235" s="10" t="s">
         <v>1360</v>
       </c>
       <c r="S235" s="3" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="T235" s="3" t="s">
         <v>225</v>
@@ -47705,7 +47717,7 @@
         <v>222</v>
       </c>
       <c r="AB235" s="3" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="AC235" s="3" t="s">
         <v>230</v>
@@ -47783,22 +47795,22 @@
         <v>169</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="D236" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H236" s="3" t="s">
         <v>222</v>
@@ -47828,13 +47840,13 @@
         <v>226</v>
       </c>
       <c r="Q236" s="3" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="R236" s="10" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="S236" s="3" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="T236" s="3" t="s">
         <v>225</v>
@@ -47861,7 +47873,7 @@
         <v>222</v>
       </c>
       <c r="AB236" s="3" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="AC236" s="3" t="s">
         <v>230</v>
@@ -47870,7 +47882,7 @@
         <v>0</v>
       </c>
       <c r="AE236" s="3" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="AF236" s="3" t="s">
         <v>230</v>
@@ -47941,22 +47953,22 @@
         <v>169</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="D237" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H237" s="3" t="s">
         <v>222</v>
@@ -47968,7 +47980,7 @@
         <v>265</v>
       </c>
       <c r="K237" s="3" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="L237" s="3" t="s">
         <v>230</v>
@@ -47986,13 +47998,13 @@
         <v>226</v>
       </c>
       <c r="Q237" s="3" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="R237" s="10" t="s">
         <v>546</v>
       </c>
       <c r="S237" s="3" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="T237" s="3" t="s">
         <v>225</v>
@@ -48019,7 +48031,7 @@
         <v>222</v>
       </c>
       <c r="AB237" s="3" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="AC237" s="3" t="s">
         <v>230</v>
@@ -48028,7 +48040,7 @@
         <v>0</v>
       </c>
       <c r="AE237" s="3" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="AF237" s="3" t="s">
         <v>230</v>
@@ -48097,22 +48109,22 @@
         <v>169</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="D238" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H238" s="3" t="s">
         <v>222</v>
@@ -48142,13 +48154,13 @@
         <v>226</v>
       </c>
       <c r="Q238" s="3" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="R238" s="10" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="S238" s="3" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="T238" s="3" t="s">
         <v>225</v>
@@ -48175,7 +48187,7 @@
         <v>222</v>
       </c>
       <c r="AB238" s="3" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="AC238" s="3" t="s">
         <v>230</v>
@@ -48184,7 +48196,7 @@
         <v>0</v>
       </c>
       <c r="AE238" s="3" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="AF238" s="3" t="s">
         <v>230</v>
@@ -48255,22 +48267,22 @@
         <v>169</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="D239" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H239" s="3" t="s">
         <v>222</v>
@@ -48300,10 +48312,10 @@
         <v>226</v>
       </c>
       <c r="Q239" s="3" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
       <c r="R239" s="10" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="S239" s="3" t="s">
         <v>485</v>
@@ -48330,10 +48342,10 @@
         <v>233</v>
       </c>
       <c r="AA239" s="10" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
       <c r="AB239" s="3" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="AC239" s="3" t="s">
         <v>225</v>
@@ -48342,7 +48354,7 @@
         <v>25000</v>
       </c>
       <c r="AE239" s="3" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
       <c r="AF239" s="3" t="s">
         <v>225</v>
@@ -48411,22 +48423,22 @@
         <v>169</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="D240" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H240" s="3" t="s">
         <v>222</v>
@@ -48456,13 +48468,13 @@
         <v>226</v>
       </c>
       <c r="Q240" s="3" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="R240" s="10" t="s">
         <v>378</v>
       </c>
       <c r="S240" s="3" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
       <c r="T240" s="3" t="s">
         <v>230</v>
@@ -48474,7 +48486,7 @@
         <v>225</v>
       </c>
       <c r="W240" s="3" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="X240" s="10" t="s">
         <v>248</v>
@@ -48489,7 +48501,7 @@
         <v>248</v>
       </c>
       <c r="AB240" s="3" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="AC240" s="3" t="s">
         <v>225</v>
@@ -48498,7 +48510,7 @@
         <v>17500</v>
       </c>
       <c r="AE240" s="3" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="AF240" s="3" t="s">
         <v>225</v>
@@ -48561,7 +48573,7 @@
         <v>6260587000</v>
       </c>
       <c r="AZ240" s="10" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="241">
@@ -48569,22 +48581,22 @@
         <v>169</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="D241" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="F241" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H241" s="3" t="s">
         <v>222</v>
@@ -48596,7 +48608,7 @@
         <v>265</v>
       </c>
       <c r="K241" s="3" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="L241" s="3" t="s">
         <v>230</v>
@@ -48614,13 +48626,13 @@
         <v>226</v>
       </c>
       <c r="Q241" s="3" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="R241" s="10" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="S241" s="3" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="T241" s="3" t="s">
         <v>230</v>
@@ -48647,7 +48659,7 @@
         <v>880</v>
       </c>
       <c r="AB241" s="3" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="AC241" s="3" t="s">
         <v>225</v>
@@ -48656,7 +48668,7 @@
         <v>30000</v>
       </c>
       <c r="AE241" s="3" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="AF241" s="3" t="s">
         <v>230</v>
@@ -48719,7 +48731,7 @@
         <v>0</v>
       </c>
       <c r="AZ241" s="10" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="242">
@@ -48727,22 +48739,22 @@
         <v>169</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="D242" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H242" s="3" t="s">
         <v>222</v>
@@ -48772,13 +48784,13 @@
         <v>571</v>
       </c>
       <c r="Q242" s="3" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="R242" s="10" t="s">
         <v>235</v>
       </c>
       <c r="S242" s="3" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="T242" s="3" t="s">
         <v>230</v>
@@ -48805,7 +48817,7 @@
         <v>233</v>
       </c>
       <c r="AB242" s="3" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="AC242" s="3" t="s">
         <v>225</v>
@@ -48814,7 +48826,7 @@
         <v>42000</v>
       </c>
       <c r="AE242" s="3" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="AF242" s="3" t="s">
         <v>225</v>
@@ -48885,22 +48897,22 @@
         <v>169</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="D243" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H243" s="3" t="s">
         <v>222</v>
@@ -48930,13 +48942,13 @@
         <v>278</v>
       </c>
       <c r="Q243" s="3" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
       <c r="R243" s="10" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="S243" s="3" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="T243" s="3" t="s">
         <v>230</v>
@@ -48960,10 +48972,10 @@
         <v>222</v>
       </c>
       <c r="AA243" s="10" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="AB243" s="3" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="AC243" s="3" t="s">
         <v>225</v>
@@ -48972,7 +48984,7 @@
         <v>57500</v>
       </c>
       <c r="AE243" s="3" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="AF243" s="3" t="s">
         <v>225</v>
@@ -49041,22 +49053,22 @@
         <v>169</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="D244" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H244" s="3" t="s">
         <v>222</v>
@@ -49068,7 +49080,7 @@
         <v>223</v>
       </c>
       <c r="K244" s="3" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="L244" s="3" t="s">
         <v>230</v>
@@ -49086,13 +49098,13 @@
         <v>226</v>
       </c>
       <c r="Q244" s="3" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="R244" s="10" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="S244" s="3" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="T244" s="3" t="s">
         <v>230</v>
@@ -49107,7 +49119,7 @@
         <v>231</v>
       </c>
       <c r="X244" s="10" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="Y244" s="10" t="s">
         <v>247</v>
@@ -49119,7 +49131,7 @@
         <v>232</v>
       </c>
       <c r="AB244" s="3" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="AC244" s="3" t="s">
         <v>225</v>
@@ -49128,7 +49140,7 @@
         <v>8000</v>
       </c>
       <c r="AE244" s="3" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="AF244" s="3" t="s">
         <v>225</v>
@@ -49149,7 +49161,7 @@
         <v>398</v>
       </c>
       <c r="AL244" s="3" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="AM244" s="10" t="n">
         <v>2153790000</v>
@@ -49191,7 +49203,7 @@
         <v>2257134000</v>
       </c>
       <c r="AZ244" s="10" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="245">
@@ -49199,22 +49211,22 @@
         <v>169</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="D245" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H245" s="3" t="s">
         <v>222</v>
@@ -49244,13 +49256,13 @@
         <v>226</v>
       </c>
       <c r="Q245" s="3" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="R245" s="10" t="s">
         <v>1472</v>
       </c>
       <c r="S245" s="3" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="T245" s="3" t="s">
         <v>230</v>
@@ -49274,10 +49286,10 @@
         <v>234</v>
       </c>
       <c r="AA245" s="10" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="AB245" s="3" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="AC245" s="3" t="s">
         <v>225</v>
@@ -49286,7 +49298,7 @@
         <v>75000</v>
       </c>
       <c r="AE245" s="3" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="AF245" s="3" t="s">
         <v>225</v>
@@ -49349,7 +49361,7 @@
         <v>4621317</v>
       </c>
       <c r="AZ245" s="10" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="246">
@@ -49357,22 +49369,22 @@
         <v>169</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="D246" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H246" s="3" t="s">
         <v>222</v>
@@ -49402,13 +49414,13 @@
         <v>226</v>
       </c>
       <c r="Q246" s="3" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="R246" s="10" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="S246" s="3" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="T246" s="3" t="s">
         <v>230</v>
@@ -49429,13 +49441,13 @@
         <v>234</v>
       </c>
       <c r="Z246" s="10" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="AA246" s="10" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="AB246" s="3" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="AC246" s="3" t="s">
         <v>225</v>
@@ -49507,7 +49519,7 @@
         <v>3415546</v>
       </c>
       <c r="AZ246" s="10" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="247">
@@ -49515,22 +49527,22 @@
         <v>169</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="D247" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H247" s="3" t="s">
         <v>222</v>
@@ -49560,13 +49572,13 @@
         <v>226</v>
       </c>
       <c r="Q247" s="3" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="R247" s="10" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="S247" s="3" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="T247" s="3" t="s">
         <v>230</v>
@@ -49593,7 +49605,7 @@
         <v>1237</v>
       </c>
       <c r="AB247" s="3" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="AC247" s="3" t="s">
         <v>225</v>
@@ -49602,7 +49614,7 @@
         <v>112500</v>
       </c>
       <c r="AE247" s="3" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="AF247" s="3" t="s">
         <v>225</v>
@@ -49671,22 +49683,22 @@
         <v>169</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="D248" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H248" s="3" t="s">
         <v>222</v>
@@ -49716,13 +49728,13 @@
         <v>226</v>
       </c>
       <c r="Q248" s="3" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="R248" s="10" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="S248" s="3" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="T248" s="3" t="s">
         <v>225</v>
@@ -49749,7 +49761,7 @@
         <v>233</v>
       </c>
       <c r="AB248" s="3" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="AC248" s="3" t="s">
         <v>225</v>
@@ -49758,7 +49770,7 @@
         <v>52000</v>
       </c>
       <c r="AE248" s="3" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="AF248" s="3" t="s">
         <v>225</v>
@@ -49829,25 +49841,25 @@
         <v>169</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="D249" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H249" s="3" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="I249" s="3" t="s">
         <v>171</v>
@@ -49874,13 +49886,13 @@
         <v>255</v>
       </c>
       <c r="Q249" s="3" t="s">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="R249" s="10" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="S249" s="3" t="s">
-        <v>2468</v>
+        <v>2469</v>
       </c>
       <c r="T249" s="3" t="s">
         <v>230</v>
@@ -49907,7 +49919,7 @@
         <v>222</v>
       </c>
       <c r="AB249" s="3" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="AC249" s="3" t="s">
         <v>225</v>
@@ -49979,7 +49991,7 @@
         <v>0</v>
       </c>
       <c r="AZ249" s="10" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="250">
@@ -49987,22 +49999,22 @@
         <v>169</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="D250" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H250" s="3" t="s">
         <v>222</v>
@@ -50032,13 +50044,13 @@
         <v>226</v>
       </c>
       <c r="Q250" s="3" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="R250" s="10" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="S250" s="3" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="T250" s="3" t="s">
         <v>230</v>
@@ -50053,7 +50065,7 @@
         <v>231</v>
       </c>
       <c r="X250" s="10" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="Y250" s="10" t="s">
         <v>222</v>
@@ -50065,7 +50077,7 @@
         <v>222</v>
       </c>
       <c r="AB250" s="3" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="AC250" s="3" t="s">
         <v>230</v>
@@ -50145,22 +50157,22 @@
         <v>169</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
       <c r="D251" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>2481</v>
+        <v>2482</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H251" s="3" t="s">
         <v>222</v>
@@ -50190,13 +50202,13 @@
         <v>278</v>
       </c>
       <c r="Q251" s="3" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
       <c r="R251" s="10" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="S251" s="3" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="T251" s="3" t="s">
         <v>230</v>
@@ -50223,7 +50235,7 @@
         <v>222</v>
       </c>
       <c r="AB251" s="3" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="AC251" s="3" t="s">
         <v>230</v>
@@ -50301,22 +50313,22 @@
         <v>169</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="D252" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="H252" s="3" t="s">
         <v>222</v>
@@ -50346,13 +50358,13 @@
         <v>226</v>
       </c>
       <c r="Q252" s="3" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="R252" s="10" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="S252" s="3" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="T252" s="3" t="s">
         <v>230</v>
@@ -50379,7 +50391,7 @@
         <v>233</v>
       </c>
       <c r="AB252" s="3" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="AC252" s="3" t="s">
         <v>225</v>
@@ -50388,7 +50400,7 @@
         <v>46086</v>
       </c>
       <c r="AE252" s="3" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="AF252" s="3" t="s">
         <v>225</v>
@@ -50459,22 +50471,22 @@
         <v>169</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="D253" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>199</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="H253" s="3" t="s">
         <v>222</v>
@@ -50501,16 +50513,16 @@
         <v>222</v>
       </c>
       <c r="P253" s="3" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="Q253" s="3" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="R253" s="10" t="s">
         <v>228</v>
       </c>
       <c r="S253" s="3" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="T253" s="3" t="s">
         <v>225</v>
@@ -50537,7 +50549,7 @@
         <v>248</v>
       </c>
       <c r="AB253" s="3" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="AC253" s="3" t="s">
         <v>230</v>
@@ -50546,7 +50558,7 @@
         <v>0</v>
       </c>
       <c r="AE253" s="3" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="AF253" s="3" t="s">
         <v>230</v>
@@ -50558,7 +50570,7 @@
         <v>0</v>
       </c>
       <c r="AI253" s="3" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="AJ253" s="3" t="s">
         <v>230</v>
@@ -50615,20 +50627,20 @@
         <v>169</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="C254" s="3"/>
       <c r="D254" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>199</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="H254" s="3" t="s">
         <v>222</v>
@@ -50658,13 +50670,13 @@
         <v>278</v>
       </c>
       <c r="Q254" s="3" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="R254" s="10" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="S254" s="3" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="T254" s="3" t="s">
         <v>230</v>
@@ -50676,7 +50688,7 @@
         <v>225</v>
       </c>
       <c r="W254" s="3" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="X254" s="10" t="s">
         <v>222</v>
@@ -50688,10 +50700,10 @@
         <v>222</v>
       </c>
       <c r="AA254" s="10" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="AB254" s="3" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="AC254" s="3" t="s">
         <v>225</v>
@@ -50700,7 +50712,7 @@
         <v>145077.6</v>
       </c>
       <c r="AE254" s="3" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="AF254" s="3" t="s">
         <v>225</v>
@@ -50712,7 +50724,7 @@
         <v>36</v>
       </c>
       <c r="AI254" s="3" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="AJ254" s="3" t="s">
         <v>230</v>
@@ -50721,7 +50733,7 @@
         <v>398</v>
       </c>
       <c r="AL254" s="3" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="AM254" s="10" t="n">
         <v>0</v>
@@ -50769,22 +50781,22 @@
         <v>169</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="D255" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>199</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="H255" s="3" t="s">
         <v>222</v>
@@ -50811,16 +50823,16 @@
         <v>222</v>
       </c>
       <c r="P255" s="3" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="Q255" s="3" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="R255" s="10" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="S255" s="3" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="T255" s="3" t="s">
         <v>230</v>
@@ -50847,7 +50859,7 @@
         <v>248</v>
       </c>
       <c r="AB255" s="3" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="AC255" s="3" t="s">
         <v>225</v>
@@ -50856,7 +50868,7 @@
         <v>80000</v>
       </c>
       <c r="AE255" s="3" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="AF255" s="3" t="s">
         <v>225</v>
@@ -50868,7 +50880,7 @@
         <v>0</v>
       </c>
       <c r="AI255" s="3" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="AJ255" s="3" t="s">
         <v>230</v>
@@ -50925,22 +50937,22 @@
         <v>169</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="D256" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>199</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="H256" s="3" t="s">
         <v>222</v>
@@ -50967,16 +50979,16 @@
         <v>222</v>
       </c>
       <c r="P256" s="3" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="Q256" s="3" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="R256" s="10" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="S256" s="3" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="T256" s="3" t="s">
         <v>230</v>
@@ -51003,7 +51015,7 @@
         <v>248</v>
       </c>
       <c r="AB256" s="3" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="AC256" s="3" t="s">
         <v>225</v>
@@ -51012,7 +51024,7 @@
         <v>35000</v>
       </c>
       <c r="AE256" s="3" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="AF256" s="3" t="s">
         <v>230</v>
@@ -51024,7 +51036,7 @@
         <v>0.37</v>
       </c>
       <c r="AI256" s="3" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="AJ256" s="3" t="s">
         <v>230</v>
@@ -51075,7 +51087,7 @@
         <v>740129</v>
       </c>
       <c r="AZ256" s="10" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="257">
@@ -51083,22 +51095,22 @@
         <v>169</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="D257" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>200</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="H257" s="3" t="s">
         <v>222</v>
@@ -51128,13 +51140,13 @@
         <v>930</v>
       </c>
       <c r="Q257" s="3" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="R257" s="10" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="S257" s="3" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="T257" s="3" t="s">
         <v>225</v>
@@ -51161,7 +51173,7 @@
         <v>234</v>
       </c>
       <c r="AB257" s="3" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
       <c r="AC257" s="3" t="s">
         <v>468</v>
@@ -51170,7 +51182,7 @@
         <v>0</v>
       </c>
       <c r="AE257" s="3" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="AF257" s="3" t="s">
         <v>230</v>
@@ -51233,7 +51245,7 @@
         <v>302000</v>
       </c>
       <c r="AZ257" s="10" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="258">
@@ -51244,22 +51256,22 @@
         <v>201</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
       <c r="D258" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>201</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="H258" s="3" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="I258" s="3" t="s">
         <v>175</v>
@@ -51286,7 +51298,7 @@
         <v>571</v>
       </c>
       <c r="Q258" s="3" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="R258" s="10" t="s">
         <v>822</v>
@@ -51313,13 +51325,13 @@
         <v>233</v>
       </c>
       <c r="Z258" s="10" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="AA258" s="10" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="AB258" s="3" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="AC258" s="3" t="s">
         <v>222</v>
@@ -51328,7 +51340,7 @@
         <v>0</v>
       </c>
       <c r="AE258" s="3" t="s">
-        <v>2539</v>
+        <v>2540</v>
       </c>
       <c r="AF258" s="3" t="s">
         <v>225</v>
@@ -51391,7 +51403,7 @@
         <v>17970000</v>
       </c>
       <c r="AZ258" s="10" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
     </row>
   </sheetData>
@@ -51419,7 +51431,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="2">
@@ -51429,7 +51441,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="4">
@@ -51439,10 +51451,10 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>41</v>
@@ -51450,46 +51462,57 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>2553</v>
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>2555</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>2547</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>2556</v>
       </c>
     </row>
   </sheetData>
